--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -484,10 +484,10 @@
     <t>['43', '66', '74']</t>
   </si>
   <si>
-    <t>['10', '67', '73']</t>
+    <t>['61', '63', '82']</t>
   </si>
   <si>
-    <t>['61', '63', '82']</t>
+    <t>['10', '67', '73']</t>
   </si>
   <si>
     <t>['47', '67']</t>
@@ -715,10 +715,10 @@
     <t>['15', '22', '44', '58', '77']</t>
   </si>
   <si>
-    <t>['25', '34', '63', '82']</t>
+    <t>['20']</t>
   </si>
   <si>
-    <t>['20']</t>
+    <t>['25', '34', '63', '82']</t>
   </si>
   <si>
     <t>['54', '78']</t>
@@ -17058,7 +17058,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>7466132</v>
+        <v>7466131</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -17070,193 +17070,193 @@
         <v>45585.39583333334</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H78" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N78">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="P78" t="s">
         <v>233</v>
       </c>
       <c r="Q78">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="R78">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="T78">
+        <v>1.36</v>
+      </c>
+      <c r="U78">
+        <v>3</v>
+      </c>
+      <c r="V78">
+        <v>2.63</v>
+      </c>
+      <c r="W78">
+        <v>1.44</v>
+      </c>
+      <c r="X78">
+        <v>7</v>
+      </c>
+      <c r="Y78">
+        <v>1.1</v>
+      </c>
+      <c r="Z78">
+        <v>3.07</v>
+      </c>
+      <c r="AA78">
+        <v>3.6</v>
+      </c>
+      <c r="AB78">
+        <v>2.12</v>
+      </c>
+      <c r="AC78">
+        <v>1.04</v>
+      </c>
+      <c r="AD78">
+        <v>13</v>
+      </c>
+      <c r="AE78">
+        <v>1.24</v>
+      </c>
+      <c r="AF78">
+        <v>3.92</v>
+      </c>
+      <c r="AG78">
+        <v>1.61</v>
+      </c>
+      <c r="AH78">
+        <v>2.13</v>
+      </c>
+      <c r="AI78">
+        <v>1.67</v>
+      </c>
+      <c r="AJ78">
+        <v>2.1</v>
+      </c>
+      <c r="AK78">
+        <v>1.8</v>
+      </c>
+      <c r="AL78">
         <v>1.25</v>
       </c>
-      <c r="U78">
-        <v>3.75</v>
-      </c>
-      <c r="V78">
-        <v>2.2</v>
-      </c>
-      <c r="W78">
-        <v>1.62</v>
-      </c>
-      <c r="X78">
-        <v>5</v>
-      </c>
-      <c r="Y78">
-        <v>1.17</v>
-      </c>
-      <c r="Z78">
-        <v>7.03</v>
-      </c>
-      <c r="AA78">
-        <v>5.2</v>
-      </c>
-      <c r="AB78">
-        <v>1.35</v>
-      </c>
-      <c r="AC78">
-        <v>1.01</v>
-      </c>
-      <c r="AD78">
-        <v>21</v>
-      </c>
-      <c r="AE78">
-        <v>1.14</v>
-      </c>
-      <c r="AF78">
-        <v>5.31</v>
-      </c>
-      <c r="AG78">
-        <v>1.48</v>
-      </c>
-      <c r="AH78">
-        <v>2.54</v>
-      </c>
-      <c r="AI78">
-        <v>1.75</v>
-      </c>
-      <c r="AJ78">
-        <v>2</v>
-      </c>
-      <c r="AK78">
-        <v>2.8</v>
-      </c>
-      <c r="AL78">
-        <v>1.15</v>
-      </c>
       <c r="AM78">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AN78">
         <v>1.25</v>
       </c>
       <c r="AO78">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AR78">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="AS78">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="AT78">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="AU78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV78">
         <v>3</v>
       </c>
       <c r="AW78">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY78">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ78">
+        <v>7</v>
+      </c>
+      <c r="BA78">
+        <v>4</v>
+      </c>
+      <c r="BB78">
+        <v>5</v>
+      </c>
+      <c r="BC78">
         <v>9</v>
       </c>
-      <c r="BA78">
-        <v>3</v>
-      </c>
-      <c r="BB78">
-        <v>0</v>
-      </c>
-      <c r="BC78">
-        <v>3</v>
-      </c>
       <c r="BD78">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="BE78">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="BF78">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="BG78">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BH78">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="BI78">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BJ78">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BK78">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BL78">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BM78">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BN78">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BO78">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BP78">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="79" spans="1:68">
@@ -17264,7 +17264,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>7466131</v>
+        <v>7466132</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -17276,193 +17276,193 @@
         <v>45585.39583333334</v>
       </c>
       <c r="F79">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O79" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="P79" t="s">
         <v>234</v>
       </c>
       <c r="Q79">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="R79">
+        <v>2.6</v>
+      </c>
+      <c r="S79">
+        <v>1.83</v>
+      </c>
+      <c r="T79">
+        <v>1.25</v>
+      </c>
+      <c r="U79">
+        <v>3.75</v>
+      </c>
+      <c r="V79">
         <v>2.2</v>
       </c>
-      <c r="S79">
-        <v>2.88</v>
-      </c>
-      <c r="T79">
-        <v>1.36</v>
-      </c>
-      <c r="U79">
-        <v>3</v>
-      </c>
-      <c r="V79">
-        <v>2.63</v>
-      </c>
       <c r="W79">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="X79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y79">
+        <v>1.17</v>
+      </c>
+      <c r="Z79">
+        <v>7.03</v>
+      </c>
+      <c r="AA79">
+        <v>5.2</v>
+      </c>
+      <c r="AB79">
+        <v>1.35</v>
+      </c>
+      <c r="AC79">
+        <v>1.01</v>
+      </c>
+      <c r="AD79">
+        <v>21</v>
+      </c>
+      <c r="AE79">
+        <v>1.14</v>
+      </c>
+      <c r="AF79">
+        <v>5.31</v>
+      </c>
+      <c r="AG79">
+        <v>1.48</v>
+      </c>
+      <c r="AH79">
+        <v>2.54</v>
+      </c>
+      <c r="AI79">
+        <v>1.75</v>
+      </c>
+      <c r="AJ79">
+        <v>2</v>
+      </c>
+      <c r="AK79">
+        <v>2.8</v>
+      </c>
+      <c r="AL79">
+        <v>1.15</v>
+      </c>
+      <c r="AM79">
         <v>1.1</v>
-      </c>
-      <c r="Z79">
-        <v>3.07</v>
-      </c>
-      <c r="AA79">
-        <v>3.6</v>
-      </c>
-      <c r="AB79">
-        <v>2.12</v>
-      </c>
-      <c r="AC79">
-        <v>1.04</v>
-      </c>
-      <c r="AD79">
-        <v>13</v>
-      </c>
-      <c r="AE79">
-        <v>1.24</v>
-      </c>
-      <c r="AF79">
-        <v>3.92</v>
-      </c>
-      <c r="AG79">
-        <v>1.61</v>
-      </c>
-      <c r="AH79">
-        <v>2.13</v>
-      </c>
-      <c r="AI79">
-        <v>1.67</v>
-      </c>
-      <c r="AJ79">
-        <v>2.1</v>
-      </c>
-      <c r="AK79">
-        <v>1.8</v>
-      </c>
-      <c r="AL79">
-        <v>1.25</v>
-      </c>
-      <c r="AM79">
-        <v>1.32</v>
       </c>
       <c r="AN79">
         <v>1.25</v>
       </c>
       <c r="AO79">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AP79">
+        <v>1.25</v>
+      </c>
+      <c r="AQ79">
+        <v>1.89</v>
+      </c>
+      <c r="AR79">
+        <v>1.54</v>
+      </c>
+      <c r="AS79">
+        <v>1.61</v>
+      </c>
+      <c r="AT79">
+        <v>3.15</v>
+      </c>
+      <c r="AU79">
+        <v>3</v>
+      </c>
+      <c r="AV79">
+        <v>3</v>
+      </c>
+      <c r="AW79">
+        <v>3</v>
+      </c>
+      <c r="AX79">
+        <v>6</v>
+      </c>
+      <c r="AY79">
+        <v>6</v>
+      </c>
+      <c r="AZ79">
+        <v>9</v>
+      </c>
+      <c r="BA79">
+        <v>3</v>
+      </c>
+      <c r="BB79">
+        <v>0</v>
+      </c>
+      <c r="BC79">
+        <v>3</v>
+      </c>
+      <c r="BD79">
+        <v>6</v>
+      </c>
+      <c r="BE79">
+        <v>10</v>
+      </c>
+      <c r="BF79">
+        <v>1.2</v>
+      </c>
+      <c r="BG79">
+        <v>1.14</v>
+      </c>
+      <c r="BH79">
+        <v>4.2</v>
+      </c>
+      <c r="BI79">
+        <v>1.36</v>
+      </c>
+      <c r="BJ79">
+        <v>3</v>
+      </c>
+      <c r="BK79">
+        <v>1.62</v>
+      </c>
+      <c r="BL79">
+        <v>2.3</v>
+      </c>
+      <c r="BM79">
+        <v>1.96</v>
+      </c>
+      <c r="BN79">
+        <v>1.78</v>
+      </c>
+      <c r="BO79">
+        <v>2.5</v>
+      </c>
+      <c r="BP79">
         <v>1.5</v>
-      </c>
-      <c r="AQ79">
-        <v>2.5</v>
-      </c>
-      <c r="AR79">
-        <v>1.07</v>
-      </c>
-      <c r="AS79">
-        <v>1.19</v>
-      </c>
-      <c r="AT79">
-        <v>2.26</v>
-      </c>
-      <c r="AU79">
-        <v>5</v>
-      </c>
-      <c r="AV79">
-        <v>3</v>
-      </c>
-      <c r="AW79">
-        <v>6</v>
-      </c>
-      <c r="AX79">
-        <v>4</v>
-      </c>
-      <c r="AY79">
-        <v>11</v>
-      </c>
-      <c r="AZ79">
-        <v>7</v>
-      </c>
-      <c r="BA79">
-        <v>4</v>
-      </c>
-      <c r="BB79">
-        <v>5</v>
-      </c>
-      <c r="BC79">
-        <v>9</v>
-      </c>
-      <c r="BD79">
-        <v>2.25</v>
-      </c>
-      <c r="BE79">
-        <v>6.5</v>
-      </c>
-      <c r="BF79">
-        <v>2</v>
-      </c>
-      <c r="BG79">
-        <v>1.15</v>
-      </c>
-      <c r="BH79">
-        <v>4.05</v>
-      </c>
-      <c r="BI79">
-        <v>1.38</v>
-      </c>
-      <c r="BJ79">
-        <v>2.9</v>
-      </c>
-      <c r="BK79">
-        <v>1.63</v>
-      </c>
-      <c r="BL79">
-        <v>2.2</v>
-      </c>
-      <c r="BM79">
-        <v>2</v>
-      </c>
-      <c r="BN79">
-        <v>1.75</v>
-      </c>
-      <c r="BO79">
-        <v>2.55</v>
-      </c>
-      <c r="BP79">
-        <v>1.48</v>
       </c>
     </row>
     <row r="80" spans="1:68">
@@ -20354,7 +20354,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>7466147</v>
+        <v>7466143</v>
       </c>
       <c r="C94" t="s">
         <v>68</v>
@@ -20366,19 +20366,19 @@
         <v>45598.70833333334</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H94" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94">
         <v>1</v>
@@ -20387,172 +20387,172 @@
         <v>3</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O94" t="s">
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="Q94">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R94">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S94">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="T94">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V94">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="W94">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="X94">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="Y94">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z94">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="AA94">
-        <v>3.33</v>
+        <v>3.77</v>
       </c>
       <c r="AB94">
-        <v>3.05</v>
+        <v>5.84</v>
       </c>
       <c r="AC94">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD94">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE94">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
-        <v>3.92</v>
+        <v>4.65</v>
       </c>
       <c r="AG94">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="AH94">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AI94">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AJ94">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AK94">
+        <v>1.14</v>
+      </c>
+      <c r="AL94">
+        <v>1.18</v>
+      </c>
+      <c r="AM94">
+        <v>2.5</v>
+      </c>
+      <c r="AN94">
+        <v>1.75</v>
+      </c>
+      <c r="AO94">
+        <v>2</v>
+      </c>
+      <c r="AP94">
+        <v>2.13</v>
+      </c>
+      <c r="AQ94">
+        <v>2</v>
+      </c>
+      <c r="AR94">
+        <v>1.67</v>
+      </c>
+      <c r="AS94">
+        <v>1.56</v>
+      </c>
+      <c r="AT94">
+        <v>3.23</v>
+      </c>
+      <c r="AU94">
+        <v>5</v>
+      </c>
+      <c r="AV94">
+        <v>6</v>
+      </c>
+      <c r="AW94">
+        <v>7</v>
+      </c>
+      <c r="AX94">
+        <v>3</v>
+      </c>
+      <c r="AY94">
+        <v>17</v>
+      </c>
+      <c r="AZ94">
+        <v>10</v>
+      </c>
+      <c r="BA94">
+        <v>10</v>
+      </c>
+      <c r="BB94">
+        <v>0</v>
+      </c>
+      <c r="BC94">
+        <v>10</v>
+      </c>
+      <c r="BD94">
         <v>1.38</v>
       </c>
-      <c r="AL94">
-        <v>1.25</v>
-      </c>
-      <c r="AM94">
-        <v>1.7</v>
-      </c>
-      <c r="AN94">
-        <v>1.8</v>
-      </c>
-      <c r="AO94">
-        <v>0</v>
-      </c>
-      <c r="AP94">
+      <c r="BE94">
+        <v>7</v>
+      </c>
+      <c r="BF94">
+        <v>3.4</v>
+      </c>
+      <c r="BG94">
+        <v>1.23</v>
+      </c>
+      <c r="BH94">
+        <v>3.65</v>
+      </c>
+      <c r="BI94">
+        <v>1.41</v>
+      </c>
+      <c r="BJ94">
+        <v>2.65</v>
+      </c>
+      <c r="BK94">
+        <v>1.66</v>
+      </c>
+      <c r="BL94">
+        <v>2.06</v>
+      </c>
+      <c r="BM94">
+        <v>2.04</v>
+      </c>
+      <c r="BN94">
         <v>1.67</v>
       </c>
-      <c r="AQ94">
-        <v>0.33</v>
-      </c>
-      <c r="AR94">
-        <v>1.29</v>
-      </c>
-      <c r="AS94">
-        <v>1.21</v>
-      </c>
-      <c r="AT94">
-        <v>2.5</v>
-      </c>
-      <c r="AU94">
-        <v>4</v>
-      </c>
-      <c r="AV94">
-        <v>3</v>
-      </c>
-      <c r="AW94">
-        <v>2</v>
-      </c>
-      <c r="AX94">
-        <v>4</v>
-      </c>
-      <c r="AY94">
-        <v>7</v>
-      </c>
-      <c r="AZ94">
-        <v>12</v>
-      </c>
-      <c r="BA94">
-        <v>1</v>
-      </c>
-      <c r="BB94">
-        <v>8</v>
-      </c>
-      <c r="BC94">
-        <v>9</v>
-      </c>
-      <c r="BD94">
-        <v>1.67</v>
-      </c>
-      <c r="BE94">
-        <v>6.75</v>
-      </c>
-      <c r="BF94">
-        <v>2.4</v>
-      </c>
-      <c r="BG94">
-        <v>1.15</v>
-      </c>
-      <c r="BH94">
-        <v>4.6</v>
-      </c>
-      <c r="BI94">
-        <v>1.26</v>
-      </c>
-      <c r="BJ94">
-        <v>3.4</v>
-      </c>
-      <c r="BK94">
-        <v>1.46</v>
-      </c>
-      <c r="BL94">
-        <v>2.5</v>
-      </c>
-      <c r="BM94">
-        <v>1.72</v>
-      </c>
-      <c r="BN94">
-        <v>1.98</v>
-      </c>
       <c r="BO94">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="BP94">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="95" spans="1:68">
@@ -20560,7 +20560,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>7466143</v>
+        <v>7466147</v>
       </c>
       <c r="C95" t="s">
         <v>68</v>
@@ -20572,19 +20572,19 @@
         <v>45598.70833333334</v>
       </c>
       <c r="F95">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95">
         <v>1</v>
@@ -20593,172 +20593,172 @@
         <v>3</v>
       </c>
       <c r="M95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N95">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O95" t="s">
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="Q95">
+        <v>2.75</v>
+      </c>
+      <c r="R95">
+        <v>2.2</v>
+      </c>
+      <c r="S95">
+        <v>3.75</v>
+      </c>
+      <c r="T95">
+        <v>1.4</v>
+      </c>
+      <c r="U95">
+        <v>2.75</v>
+      </c>
+      <c r="V95">
+        <v>2.75</v>
+      </c>
+      <c r="W95">
+        <v>1.4</v>
+      </c>
+      <c r="X95">
+        <v>8</v>
+      </c>
+      <c r="Y95">
+        <v>1.08</v>
+      </c>
+      <c r="Z95">
+        <v>2.12</v>
+      </c>
+      <c r="AA95">
+        <v>3.33</v>
+      </c>
+      <c r="AB95">
+        <v>3.05</v>
+      </c>
+      <c r="AC95">
+        <v>1.04</v>
+      </c>
+      <c r="AD95">
+        <v>13</v>
+      </c>
+      <c r="AE95">
+        <v>1.24</v>
+      </c>
+      <c r="AF95">
+        <v>3.92</v>
+      </c>
+      <c r="AG95">
+        <v>1.89</v>
+      </c>
+      <c r="AH95">
+        <v>1.92</v>
+      </c>
+      <c r="AI95">
+        <v>1.7</v>
+      </c>
+      <c r="AJ95">
         <v>2.05</v>
       </c>
-      <c r="R95">
+      <c r="AK95">
+        <v>1.38</v>
+      </c>
+      <c r="AL95">
+        <v>1.25</v>
+      </c>
+      <c r="AM95">
+        <v>1.7</v>
+      </c>
+      <c r="AN95">
+        <v>1.8</v>
+      </c>
+      <c r="AO95">
+        <v>0</v>
+      </c>
+      <c r="AP95">
+        <v>1.67</v>
+      </c>
+      <c r="AQ95">
+        <v>0.33</v>
+      </c>
+      <c r="AR95">
+        <v>1.29</v>
+      </c>
+      <c r="AS95">
+        <v>1.21</v>
+      </c>
+      <c r="AT95">
         <v>2.5</v>
       </c>
-      <c r="S95">
-        <v>5.5</v>
-      </c>
-      <c r="T95">
-        <v>1.29</v>
-      </c>
-      <c r="U95">
-        <v>3.5</v>
-      </c>
-      <c r="V95">
-        <v>2.25</v>
-      </c>
-      <c r="W95">
-        <v>1.57</v>
-      </c>
-      <c r="X95">
-        <v>5.5</v>
-      </c>
-      <c r="Y95">
-        <v>1.14</v>
-      </c>
-      <c r="Z95">
-        <v>1.51</v>
-      </c>
-      <c r="AA95">
-        <v>3.77</v>
-      </c>
-      <c r="AB95">
-        <v>5.84</v>
-      </c>
-      <c r="AC95">
-        <v>1.03</v>
-      </c>
-      <c r="AD95">
-        <v>17</v>
-      </c>
-      <c r="AE95">
-        <v>1.18</v>
-      </c>
-      <c r="AF95">
-        <v>4.65</v>
-      </c>
-      <c r="AG95">
-        <v>1.56</v>
-      </c>
-      <c r="AH95">
-        <v>2.22</v>
-      </c>
-      <c r="AI95">
+      <c r="AU95">
+        <v>4</v>
+      </c>
+      <c r="AV95">
+        <v>3</v>
+      </c>
+      <c r="AW95">
+        <v>2</v>
+      </c>
+      <c r="AX95">
+        <v>4</v>
+      </c>
+      <c r="AY95">
+        <v>7</v>
+      </c>
+      <c r="AZ95">
+        <v>12</v>
+      </c>
+      <c r="BA95">
+        <v>1</v>
+      </c>
+      <c r="BB95">
+        <v>8</v>
+      </c>
+      <c r="BC95">
+        <v>9</v>
+      </c>
+      <c r="BD95">
         <v>1.67</v>
       </c>
-      <c r="AJ95">
-        <v>2.1</v>
-      </c>
-      <c r="AK95">
-        <v>1.14</v>
-      </c>
-      <c r="AL95">
-        <v>1.18</v>
-      </c>
-      <c r="AM95">
+      <c r="BE95">
+        <v>6.75</v>
+      </c>
+      <c r="BF95">
+        <v>2.4</v>
+      </c>
+      <c r="BG95">
+        <v>1.15</v>
+      </c>
+      <c r="BH95">
+        <v>4.6</v>
+      </c>
+      <c r="BI95">
+        <v>1.26</v>
+      </c>
+      <c r="BJ95">
+        <v>3.4</v>
+      </c>
+      <c r="BK95">
+        <v>1.46</v>
+      </c>
+      <c r="BL95">
         <v>2.5</v>
       </c>
-      <c r="AN95">
-        <v>1.75</v>
-      </c>
-      <c r="AO95">
-        <v>2</v>
-      </c>
-      <c r="AP95">
-        <v>2.13</v>
-      </c>
-      <c r="AQ95">
-        <v>2</v>
-      </c>
-      <c r="AR95">
-        <v>1.67</v>
-      </c>
-      <c r="AS95">
-        <v>1.56</v>
-      </c>
-      <c r="AT95">
-        <v>3.23</v>
-      </c>
-      <c r="AU95">
-        <v>5</v>
-      </c>
-      <c r="AV95">
-        <v>6</v>
-      </c>
-      <c r="AW95">
-        <v>7</v>
-      </c>
-      <c r="AX95">
-        <v>3</v>
-      </c>
-      <c r="AY95">
-        <v>17</v>
-      </c>
-      <c r="AZ95">
-        <v>10</v>
-      </c>
-      <c r="BA95">
-        <v>10</v>
-      </c>
-      <c r="BB95">
-        <v>0</v>
-      </c>
-      <c r="BC95">
-        <v>10</v>
-      </c>
-      <c r="BD95">
-        <v>1.38</v>
-      </c>
-      <c r="BE95">
-        <v>7</v>
-      </c>
-      <c r="BF95">
-        <v>3.4</v>
-      </c>
-      <c r="BG95">
-        <v>1.23</v>
-      </c>
-      <c r="BH95">
-        <v>3.65</v>
-      </c>
-      <c r="BI95">
-        <v>1.41</v>
-      </c>
-      <c r="BJ95">
-        <v>2.65</v>
-      </c>
-      <c r="BK95">
-        <v>1.66</v>
-      </c>
-      <c r="BL95">
-        <v>2.06</v>
-      </c>
       <c r="BM95">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="BN95">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="BO95">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="BP95">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="96" spans="1:68">
@@ -28594,7 +28594,7 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>7466180</v>
+        <v>7466187</v>
       </c>
       <c r="C134" t="s">
         <v>68</v>
@@ -28609,10 +28609,10 @@
         <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H134" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -28624,175 +28624,175 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N134">
         <v>3</v>
       </c>
       <c r="O134" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="Q134">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S134">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="T134">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="U134">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="V134">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="W134">
+        <v>1.3</v>
+      </c>
+      <c r="X134">
+        <v>10</v>
+      </c>
+      <c r="Y134">
+        <v>1.06</v>
+      </c>
+      <c r="Z134">
+        <v>2.3</v>
+      </c>
+      <c r="AA134">
+        <v>3.05</v>
+      </c>
+      <c r="AB134">
+        <v>2.7</v>
+      </c>
+      <c r="AC134">
+        <v>1.05</v>
+      </c>
+      <c r="AD134">
+        <v>9</v>
+      </c>
+      <c r="AE134">
+        <v>1.3</v>
+      </c>
+      <c r="AF134">
+        <v>3.35</v>
+      </c>
+      <c r="AG134">
+        <v>2.01</v>
+      </c>
+      <c r="AH134">
+        <v>1.71</v>
+      </c>
+      <c r="AI134">
+        <v>1.91</v>
+      </c>
+      <c r="AJ134">
+        <v>1.91</v>
+      </c>
+      <c r="AK134">
+        <v>1.42</v>
+      </c>
+      <c r="AL134">
+        <v>1.25</v>
+      </c>
+      <c r="AM134">
+        <v>1.53</v>
+      </c>
+      <c r="AN134">
+        <v>1.14</v>
+      </c>
+      <c r="AO134">
+        <v>0</v>
+      </c>
+      <c r="AP134">
+        <v>1.22</v>
+      </c>
+      <c r="AQ134">
+        <v>0.33</v>
+      </c>
+      <c r="AR134">
+        <v>1.12</v>
+      </c>
+      <c r="AS134">
+        <v>1.2</v>
+      </c>
+      <c r="AT134">
+        <v>2.32</v>
+      </c>
+      <c r="AU134">
+        <v>4</v>
+      </c>
+      <c r="AV134">
+        <v>5</v>
+      </c>
+      <c r="AW134">
+        <v>6</v>
+      </c>
+      <c r="AX134">
+        <v>7</v>
+      </c>
+      <c r="AY134">
+        <v>10</v>
+      </c>
+      <c r="AZ134">
+        <v>21</v>
+      </c>
+      <c r="BA134">
+        <v>2</v>
+      </c>
+      <c r="BB134">
+        <v>3</v>
+      </c>
+      <c r="BC134">
+        <v>5</v>
+      </c>
+      <c r="BD134">
+        <v>2.02</v>
+      </c>
+      <c r="BE134">
+        <v>6.4</v>
+      </c>
+      <c r="BF134">
+        <v>1.98</v>
+      </c>
+      <c r="BG134">
+        <v>1.25</v>
+      </c>
+      <c r="BH134">
+        <v>3.45</v>
+      </c>
+      <c r="BI134">
         <v>1.44</v>
       </c>
-      <c r="X134">
-        <v>6.5</v>
-      </c>
-      <c r="Y134">
-        <v>1.11</v>
-      </c>
-      <c r="Z134">
-        <v>2.8</v>
-      </c>
-      <c r="AA134">
-        <v>3.45</v>
-      </c>
-      <c r="AB134">
-        <v>2.4</v>
-      </c>
-      <c r="AC134">
-        <v>1.03</v>
-      </c>
-      <c r="AD134">
-        <v>15</v>
-      </c>
-      <c r="AE134">
-        <v>1.22</v>
-      </c>
-      <c r="AF134">
-        <v>4.08</v>
-      </c>
-      <c r="AG134">
-        <v>1.71</v>
-      </c>
-      <c r="AH134">
-        <v>2.14</v>
-      </c>
-      <c r="AI134">
-        <v>1.57</v>
-      </c>
-      <c r="AJ134">
-        <v>2.25</v>
-      </c>
-      <c r="AK134">
-        <v>1.68</v>
-      </c>
-      <c r="AL134">
-        <v>1.24</v>
-      </c>
-      <c r="AM134">
+      <c r="BJ134">
+        <v>2.55</v>
+      </c>
+      <c r="BK134">
+        <v>1.7</v>
+      </c>
+      <c r="BL134">
+        <v>2.05</v>
+      </c>
+      <c r="BM134">
+        <v>2.1</v>
+      </c>
+      <c r="BN134">
+        <v>1.64</v>
+      </c>
+      <c r="BO134">
+        <v>2.65</v>
+      </c>
+      <c r="BP134">
         <v>1.4</v>
-      </c>
-      <c r="AN134">
-        <v>1.43</v>
-      </c>
-      <c r="AO134">
-        <v>2</v>
-      </c>
-      <c r="AP134">
-        <v>1.78</v>
-      </c>
-      <c r="AQ134">
-        <v>1.89</v>
-      </c>
-      <c r="AR134">
-        <v>1.92</v>
-      </c>
-      <c r="AS134">
-        <v>1.38</v>
-      </c>
-      <c r="AT134">
-        <v>3.3</v>
-      </c>
-      <c r="AU134">
-        <v>5</v>
-      </c>
-      <c r="AV134">
-        <v>4</v>
-      </c>
-      <c r="AW134">
-        <v>5</v>
-      </c>
-      <c r="AX134">
-        <v>3</v>
-      </c>
-      <c r="AY134">
-        <v>13</v>
-      </c>
-      <c r="AZ134">
-        <v>9</v>
-      </c>
-      <c r="BA134">
-        <v>6</v>
-      </c>
-      <c r="BB134">
-        <v>3</v>
-      </c>
-      <c r="BC134">
-        <v>9</v>
-      </c>
-      <c r="BD134">
-        <v>2.15</v>
-      </c>
-      <c r="BE134">
-        <v>6.6</v>
-      </c>
-      <c r="BF134">
-        <v>1.95</v>
-      </c>
-      <c r="BG134">
-        <v>1.33</v>
-      </c>
-      <c r="BH134">
-        <v>2.98</v>
-      </c>
-      <c r="BI134">
-        <v>1.62</v>
-      </c>
-      <c r="BJ134">
-        <v>2.12</v>
-      </c>
-      <c r="BK134">
-        <v>2.08</v>
-      </c>
-      <c r="BL134">
-        <v>1.65</v>
-      </c>
-      <c r="BM134">
-        <v>2.9</v>
-      </c>
-      <c r="BN134">
-        <v>1.35</v>
-      </c>
-      <c r="BO134">
-        <v>4.25</v>
-      </c>
-      <c r="BP134">
-        <v>1.18</v>
       </c>
     </row>
     <row r="135" spans="1:68">
@@ -28800,7 +28800,7 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>7466187</v>
+        <v>7466180</v>
       </c>
       <c r="C135" t="s">
         <v>68</v>
@@ -28815,10 +28815,10 @@
         <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H135" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -28830,175 +28830,175 @@
         <v>0</v>
       </c>
       <c r="L135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N135">
         <v>3</v>
       </c>
       <c r="O135" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="P135" t="s">
-        <v>262</v>
+        <v>134</v>
       </c>
       <c r="Q135">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R135">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="T135">
+        <v>1.33</v>
+      </c>
+      <c r="U135">
+        <v>3.25</v>
+      </c>
+      <c r="V135">
+        <v>2.63</v>
+      </c>
+      <c r="W135">
         <v>1.44</v>
       </c>
-      <c r="U135">
-        <v>2.63</v>
-      </c>
-      <c r="V135">
-        <v>3.4</v>
-      </c>
-      <c r="W135">
-        <v>1.3</v>
-      </c>
       <c r="X135">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="Y135">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z135">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AA135">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AB135">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AC135">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD135">
+        <v>15</v>
+      </c>
+      <c r="AE135">
+        <v>1.22</v>
+      </c>
+      <c r="AF135">
+        <v>4.08</v>
+      </c>
+      <c r="AG135">
+        <v>1.71</v>
+      </c>
+      <c r="AH135">
+        <v>2.14</v>
+      </c>
+      <c r="AI135">
+        <v>1.57</v>
+      </c>
+      <c r="AJ135">
+        <v>2.25</v>
+      </c>
+      <c r="AK135">
+        <v>1.68</v>
+      </c>
+      <c r="AL135">
+        <v>1.24</v>
+      </c>
+      <c r="AM135">
+        <v>1.4</v>
+      </c>
+      <c r="AN135">
+        <v>1.43</v>
+      </c>
+      <c r="AO135">
+        <v>2</v>
+      </c>
+      <c r="AP135">
+        <v>1.78</v>
+      </c>
+      <c r="AQ135">
+        <v>1.89</v>
+      </c>
+      <c r="AR135">
+        <v>1.92</v>
+      </c>
+      <c r="AS135">
+        <v>1.38</v>
+      </c>
+      <c r="AT135">
+        <v>3.3</v>
+      </c>
+      <c r="AU135">
+        <v>5</v>
+      </c>
+      <c r="AV135">
+        <v>4</v>
+      </c>
+      <c r="AW135">
+        <v>5</v>
+      </c>
+      <c r="AX135">
+        <v>3</v>
+      </c>
+      <c r="AY135">
+        <v>13</v>
+      </c>
+      <c r="AZ135">
         <v>9</v>
       </c>
-      <c r="AE135">
-        <v>1.3</v>
-      </c>
-      <c r="AF135">
-        <v>3.35</v>
-      </c>
-      <c r="AG135">
-        <v>2.01</v>
-      </c>
-      <c r="AH135">
-        <v>1.71</v>
-      </c>
-      <c r="AI135">
-        <v>1.91</v>
-      </c>
-      <c r="AJ135">
-        <v>1.91</v>
-      </c>
-      <c r="AK135">
-        <v>1.42</v>
-      </c>
-      <c r="AL135">
-        <v>1.25</v>
-      </c>
-      <c r="AM135">
-        <v>1.53</v>
-      </c>
-      <c r="AN135">
-        <v>1.14</v>
-      </c>
-      <c r="AO135">
-        <v>0</v>
-      </c>
-      <c r="AP135">
-        <v>1.22</v>
-      </c>
-      <c r="AQ135">
-        <v>0.33</v>
-      </c>
-      <c r="AR135">
-        <v>1.12</v>
-      </c>
-      <c r="AS135">
-        <v>1.2</v>
-      </c>
-      <c r="AT135">
-        <v>2.32</v>
-      </c>
-      <c r="AU135">
-        <v>4</v>
-      </c>
-      <c r="AV135">
-        <v>5</v>
-      </c>
-      <c r="AW135">
+      <c r="BA135">
         <v>6</v>
       </c>
-      <c r="AX135">
-        <v>7</v>
-      </c>
-      <c r="AY135">
-        <v>10</v>
-      </c>
-      <c r="AZ135">
-        <v>21</v>
-      </c>
-      <c r="BA135">
-        <v>2</v>
-      </c>
       <c r="BB135">
         <v>3</v>
       </c>
       <c r="BC135">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD135">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="BE135">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF135">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="BG135">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BH135">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="BI135">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BJ135">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="BK135">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="BL135">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="BM135">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="BN135">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="BO135">
-        <v>2.65</v>
+        <v>4.25</v>
       </c>
       <c r="BP135">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="136" spans="1:68">
@@ -30242,7 +30242,7 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>7466189</v>
+        <v>7466193</v>
       </c>
       <c r="C142" t="s">
         <v>68</v>
@@ -30257,190 +30257,190 @@
         <v>16</v>
       </c>
       <c r="G142" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H142" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N142">
         <v>2</v>
       </c>
       <c r="O142" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="P142" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="Q142">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="R142">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S142">
+        <v>4</v>
+      </c>
+      <c r="T142">
+        <v>1.4</v>
+      </c>
+      <c r="U142">
+        <v>2.75</v>
+      </c>
+      <c r="V142">
+        <v>2.75</v>
+      </c>
+      <c r="W142">
+        <v>1.4</v>
+      </c>
+      <c r="X142">
+        <v>8</v>
+      </c>
+      <c r="Y142">
+        <v>1.08</v>
+      </c>
+      <c r="Z142">
+        <v>2.03</v>
+      </c>
+      <c r="AA142">
+        <v>3.1</v>
+      </c>
+      <c r="AB142">
+        <v>3.2</v>
+      </c>
+      <c r="AC142">
+        <v>1.05</v>
+      </c>
+      <c r="AD142">
+        <v>12</v>
+      </c>
+      <c r="AE142">
+        <v>1.28</v>
+      </c>
+      <c r="AF142">
+        <v>3.52</v>
+      </c>
+      <c r="AG142">
+        <v>1.85</v>
+      </c>
+      <c r="AH142">
+        <v>1.85</v>
+      </c>
+      <c r="AI142">
+        <v>1.75</v>
+      </c>
+      <c r="AJ142">
+        <v>2</v>
+      </c>
+      <c r="AK142">
+        <v>1.3</v>
+      </c>
+      <c r="AL142">
+        <v>1.26</v>
+      </c>
+      <c r="AM142">
+        <v>1.8</v>
+      </c>
+      <c r="AN142">
+        <v>1.25</v>
+      </c>
+      <c r="AO142">
+        <v>1</v>
+      </c>
+      <c r="AP142">
+        <v>1.22</v>
+      </c>
+      <c r="AQ142">
+        <v>1</v>
+      </c>
+      <c r="AR142">
+        <v>1.53</v>
+      </c>
+      <c r="AS142">
+        <v>1.24</v>
+      </c>
+      <c r="AT142">
+        <v>2.77</v>
+      </c>
+      <c r="AU142">
+        <v>8</v>
+      </c>
+      <c r="AV142">
         <v>7</v>
       </c>
-      <c r="T142">
-        <v>1.33</v>
-      </c>
-      <c r="U142">
-        <v>3.25</v>
-      </c>
-      <c r="V142">
-        <v>2.5</v>
-      </c>
-      <c r="W142">
-        <v>1.5</v>
-      </c>
-      <c r="X142">
+      <c r="AW142">
+        <v>6</v>
+      </c>
+      <c r="AX142">
+        <v>7</v>
+      </c>
+      <c r="AY142">
+        <v>22</v>
+      </c>
+      <c r="AZ142">
+        <v>17</v>
+      </c>
+      <c r="BA142">
+        <v>13</v>
+      </c>
+      <c r="BB142">
+        <v>6</v>
+      </c>
+      <c r="BC142">
+        <v>19</v>
+      </c>
+      <c r="BD142">
+        <v>1.96</v>
+      </c>
+      <c r="BE142">
         <v>6.5</v>
       </c>
-      <c r="Y142">
-        <v>1.11</v>
-      </c>
-      <c r="Z142">
+      <c r="BF142">
+        <v>2.02</v>
+      </c>
+      <c r="BG142">
+        <v>1.2</v>
+      </c>
+      <c r="BH142">
+        <v>3.95</v>
+      </c>
+      <c r="BI142">
         <v>1.35</v>
       </c>
-      <c r="AA142">
-        <v>4.5</v>
-      </c>
-      <c r="AB142">
-        <v>7.1</v>
-      </c>
-      <c r="AC142">
-        <v>1.02</v>
-      </c>
-      <c r="AD142">
-        <v>19</v>
-      </c>
-      <c r="AE142">
-        <v>1.18</v>
-      </c>
-      <c r="AF142">
-        <v>4.65</v>
-      </c>
-      <c r="AG142">
-        <v>1.6</v>
-      </c>
-      <c r="AH142">
-        <v>2.2</v>
-      </c>
-      <c r="AI142">
-        <v>1.95</v>
-      </c>
-      <c r="AJ142">
-        <v>1.8</v>
-      </c>
-      <c r="AK142">
-        <v>1.07</v>
-      </c>
-      <c r="AL142">
-        <v>1.13</v>
-      </c>
-      <c r="AM142">
-        <v>3.1</v>
-      </c>
-      <c r="AN142">
-        <v>2.14</v>
-      </c>
-      <c r="AO142">
-        <v>0.57</v>
-      </c>
-      <c r="AP142">
-        <v>2.25</v>
-      </c>
-      <c r="AQ142">
-        <v>0.5</v>
-      </c>
-      <c r="AR142">
-        <v>2.08</v>
-      </c>
-      <c r="AS142">
-        <v>1.06</v>
-      </c>
-      <c r="AT142">
-        <v>3.14</v>
-      </c>
-      <c r="AU142">
-        <v>6</v>
-      </c>
-      <c r="AV142">
-        <v>4</v>
-      </c>
-      <c r="AW142">
-        <v>4</v>
-      </c>
-      <c r="AX142">
-        <v>4</v>
-      </c>
-      <c r="AY142">
-        <v>13</v>
-      </c>
-      <c r="AZ142">
-        <v>10</v>
-      </c>
-      <c r="BA142">
-        <v>3</v>
-      </c>
-      <c r="BB142">
-        <v>5</v>
-      </c>
-      <c r="BC142">
-        <v>8</v>
-      </c>
-      <c r="BD142">
-        <v>1.3</v>
-      </c>
-      <c r="BE142">
-        <v>7.5</v>
-      </c>
-      <c r="BF142">
-        <v>3.7</v>
-      </c>
-      <c r="BG142">
-        <v>1.24</v>
-      </c>
-      <c r="BH142">
-        <v>3.55</v>
-      </c>
-      <c r="BI142">
-        <v>1.43</v>
-      </c>
       <c r="BJ142">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="BK142">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="BL142">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="BM142">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="BN142">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="BO142">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="BP142">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="143" spans="1:68">
@@ -30448,7 +30448,7 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>7466193</v>
+        <v>7466189</v>
       </c>
       <c r="C143" t="s">
         <v>68</v>
@@ -30463,190 +30463,190 @@
         <v>16</v>
       </c>
       <c r="G143" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N143">
         <v>2</v>
       </c>
       <c r="O143" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="P143" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="Q143">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="R143">
+        <v>2.4</v>
+      </c>
+      <c r="S143">
+        <v>7</v>
+      </c>
+      <c r="T143">
+        <v>1.33</v>
+      </c>
+      <c r="U143">
+        <v>3.25</v>
+      </c>
+      <c r="V143">
+        <v>2.5</v>
+      </c>
+      <c r="W143">
+        <v>1.5</v>
+      </c>
+      <c r="X143">
+        <v>6.5</v>
+      </c>
+      <c r="Y143">
+        <v>1.11</v>
+      </c>
+      <c r="Z143">
+        <v>1.35</v>
+      </c>
+      <c r="AA143">
+        <v>4.5</v>
+      </c>
+      <c r="AB143">
+        <v>7.1</v>
+      </c>
+      <c r="AC143">
+        <v>1.02</v>
+      </c>
+      <c r="AD143">
+        <v>19</v>
+      </c>
+      <c r="AE143">
+        <v>1.18</v>
+      </c>
+      <c r="AF143">
+        <v>4.65</v>
+      </c>
+      <c r="AG143">
+        <v>1.6</v>
+      </c>
+      <c r="AH143">
         <v>2.2</v>
       </c>
-      <c r="S143">
+      <c r="AI143">
+        <v>1.95</v>
+      </c>
+      <c r="AJ143">
+        <v>1.8</v>
+      </c>
+      <c r="AK143">
+        <v>1.07</v>
+      </c>
+      <c r="AL143">
+        <v>1.13</v>
+      </c>
+      <c r="AM143">
+        <v>3.1</v>
+      </c>
+      <c r="AN143">
+        <v>2.14</v>
+      </c>
+      <c r="AO143">
+        <v>0.57</v>
+      </c>
+      <c r="AP143">
+        <v>2.25</v>
+      </c>
+      <c r="AQ143">
+        <v>0.5</v>
+      </c>
+      <c r="AR143">
+        <v>2.08</v>
+      </c>
+      <c r="AS143">
+        <v>1.06</v>
+      </c>
+      <c r="AT143">
+        <v>3.14</v>
+      </c>
+      <c r="AU143">
+        <v>6</v>
+      </c>
+      <c r="AV143">
         <v>4</v>
       </c>
-      <c r="T143">
-        <v>1.4</v>
-      </c>
-      <c r="U143">
-        <v>2.75</v>
-      </c>
-      <c r="V143">
-        <v>2.75</v>
-      </c>
-      <c r="W143">
-        <v>1.4</v>
-      </c>
-      <c r="X143">
+      <c r="AW143">
+        <v>4</v>
+      </c>
+      <c r="AX143">
+        <v>4</v>
+      </c>
+      <c r="AY143">
+        <v>13</v>
+      </c>
+      <c r="AZ143">
+        <v>10</v>
+      </c>
+      <c r="BA143">
+        <v>3</v>
+      </c>
+      <c r="BB143">
+        <v>5</v>
+      </c>
+      <c r="BC143">
         <v>8</v>
       </c>
-      <c r="Y143">
-        <v>1.08</v>
-      </c>
-      <c r="Z143">
-        <v>2.03</v>
-      </c>
-      <c r="AA143">
-        <v>3.1</v>
-      </c>
-      <c r="AB143">
-        <v>3.2</v>
-      </c>
-      <c r="AC143">
-        <v>1.05</v>
-      </c>
-      <c r="AD143">
-        <v>12</v>
-      </c>
-      <c r="AE143">
-        <v>1.28</v>
-      </c>
-      <c r="AF143">
-        <v>3.52</v>
-      </c>
-      <c r="AG143">
-        <v>1.85</v>
-      </c>
-      <c r="AH143">
-        <v>1.85</v>
-      </c>
-      <c r="AI143">
-        <v>1.75</v>
-      </c>
-      <c r="AJ143">
-        <v>2</v>
-      </c>
-      <c r="AK143">
+      <c r="BD143">
         <v>1.3</v>
       </c>
-      <c r="AL143">
-        <v>1.26</v>
-      </c>
-      <c r="AM143">
-        <v>1.8</v>
-      </c>
-      <c r="AN143">
-        <v>1.25</v>
-      </c>
-      <c r="AO143">
-        <v>1</v>
-      </c>
-      <c r="AP143">
-        <v>1.22</v>
-      </c>
-      <c r="AQ143">
-        <v>1</v>
-      </c>
-      <c r="AR143">
-        <v>1.53</v>
-      </c>
-      <c r="AS143">
+      <c r="BE143">
+        <v>7.5</v>
+      </c>
+      <c r="BF143">
+        <v>3.7</v>
+      </c>
+      <c r="BG143">
         <v>1.24</v>
       </c>
-      <c r="AT143">
-        <v>2.77</v>
-      </c>
-      <c r="AU143">
-        <v>8</v>
-      </c>
-      <c r="AV143">
-        <v>7</v>
-      </c>
-      <c r="AW143">
-        <v>6</v>
-      </c>
-      <c r="AX143">
-        <v>7</v>
-      </c>
-      <c r="AY143">
-        <v>22</v>
-      </c>
-      <c r="AZ143">
-        <v>17</v>
-      </c>
-      <c r="BA143">
-        <v>13</v>
-      </c>
-      <c r="BB143">
-        <v>6</v>
-      </c>
-      <c r="BC143">
-        <v>19</v>
-      </c>
-      <c r="BD143">
-        <v>1.96</v>
-      </c>
-      <c r="BE143">
-        <v>6.5</v>
-      </c>
-      <c r="BF143">
-        <v>2.02</v>
-      </c>
-      <c r="BG143">
-        <v>1.2</v>
-      </c>
       <c r="BH143">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BI143">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="BJ143">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="BK143">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BL143">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BM143">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="BN143">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="BO143">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="BP143">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="144" spans="1:68">
@@ -32855,16 +32855,16 @@
         <v>7</v>
       </c>
       <c r="AW154">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AX154">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AY154">
+        <v>19</v>
+      </c>
+      <c r="AZ154">
         <v>22</v>
-      </c>
-      <c r="AZ154">
-        <v>27</v>
       </c>
       <c r="BA154">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="276">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,12 @@
     <t>['20', '33', '63', '86']</t>
   </si>
   <si>
+    <t>['4', '41']</t>
+  </si>
+  <si>
+    <t>['68', '85']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -827,6 +833,15 @@
   </si>
   <si>
     <t>['27', '47', '87']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['23']</t>
+  </si>
+  <si>
+    <t>['41', '74']</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1856,7 +1871,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2062,7 +2077,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2143,7 +2158,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2268,7 +2283,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2346,10 +2361,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ6">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2886,7 +2901,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3170,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ10">
         <v>0.33</v>
@@ -3997,7 +4012,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ14">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4122,7 +4137,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4328,7 +4343,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4406,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16">
         <v>2.33</v>
@@ -4534,7 +4549,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4612,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
         <v>2</v>
@@ -5358,7 +5373,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5564,7 +5579,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5851,7 +5866,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR23">
         <v>1.65</v>
@@ -6054,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24">
         <v>1.38</v>
@@ -6182,7 +6197,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6469,7 +6484,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ26">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6594,7 +6609,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6675,7 +6690,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR27">
         <v>1.81</v>
@@ -7006,7 +7021,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7087,7 +7102,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ29">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>2.19</v>
@@ -7418,7 +7433,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7624,7 +7639,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7908,7 +7923,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ33">
         <v>0.5</v>
@@ -8114,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ34">
         <v>1.22</v>
@@ -8320,10 +8335,10 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ35">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>2.65</v>
@@ -8654,7 +8669,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9066,7 +9081,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9272,7 +9287,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9559,7 +9574,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ41">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -9762,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42">
         <v>0.25</v>
@@ -10174,7 +10189,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ44">
         <v>1.11</v>
@@ -10302,7 +10317,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10380,10 +10395,10 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10508,7 +10523,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10714,7 +10729,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10920,7 +10935,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11126,7 +11141,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11332,7 +11347,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11538,7 +11553,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11950,7 +11965,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12156,7 +12171,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12234,7 +12249,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ54">
         <v>0.33</v>
@@ -12362,7 +12377,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12568,7 +12583,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13058,7 +13073,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
         <v>0.25</v>
@@ -13598,7 +13613,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13804,7 +13819,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14297,7 +14312,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ64">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>0.92</v>
@@ -14500,7 +14515,7 @@
         <v>2.33</v>
       </c>
       <c r="AP65">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14628,7 +14643,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14709,7 +14724,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ66">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR66">
         <v>1.08</v>
@@ -14834,7 +14849,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15452,7 +15467,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15530,7 +15545,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ70">
         <v>0.5</v>
@@ -15739,7 +15754,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR71">
         <v>1.43</v>
@@ -15864,7 +15879,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16070,7 +16085,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16482,7 +16497,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16688,7 +16703,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17100,7 +17115,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17306,7 +17321,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17384,7 +17399,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ79">
         <v>1.89</v>
@@ -17512,7 +17527,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17590,7 +17605,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ80">
         <v>0.78</v>
@@ -17799,7 +17814,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ81">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.25</v>
@@ -18208,7 +18223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP83">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ83">
         <v>0.5600000000000001</v>
@@ -18336,7 +18351,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18417,7 +18432,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ84">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -18748,7 +18763,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19238,7 +19253,7 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ88">
         <v>1.38</v>
@@ -19366,7 +19381,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19572,7 +19587,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19778,7 +19793,7 @@
         <v>91</v>
       </c>
       <c r="P91" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q91">
         <v>5.5</v>
@@ -20062,7 +20077,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ92">
         <v>0.78</v>
@@ -20190,7 +20205,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20268,7 +20283,7 @@
         <v>3</v>
       </c>
       <c r="AP93">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ93">
         <v>2.33</v>
@@ -20396,7 +20411,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20477,7 +20492,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ94">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -20808,7 +20823,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21220,7 +21235,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22122,7 +22137,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ102">
         <v>1.11</v>
@@ -22250,7 +22265,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22456,7 +22471,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22537,7 +22552,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ104">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.2</v>
@@ -22662,7 +22677,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22868,7 +22883,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23280,7 +23295,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23898,7 +23913,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -23976,10 +23991,10 @@
         <v>0</v>
       </c>
       <c r="AP111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ111">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR111">
         <v>1.37</v>
@@ -24182,7 +24197,7 @@
         <v>0.67</v>
       </c>
       <c r="AP112">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ112">
         <v>0.5</v>
@@ -24310,7 +24325,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24516,7 +24531,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24722,7 +24737,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24803,7 +24818,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ115">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -24928,7 +24943,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25212,7 +25227,7 @@
         <v>0.5</v>
       </c>
       <c r="AP117">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ117">
         <v>0.5600000000000001</v>
@@ -25421,7 +25436,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ118">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -26242,7 +26257,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26370,7 +26385,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26576,7 +26591,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26988,7 +27003,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27194,7 +27209,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27272,7 +27287,7 @@
         <v>2.67</v>
       </c>
       <c r="AP127">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ127">
         <v>2.5</v>
@@ -27478,7 +27493,7 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ128">
         <v>1.44</v>
@@ -27687,7 +27702,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.64</v>
@@ -27812,7 +27827,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28018,7 +28033,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28224,7 +28239,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28302,7 +28317,7 @@
         <v>0.86</v>
       </c>
       <c r="AP132">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ132">
         <v>1.11</v>
@@ -28636,7 +28651,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29048,7 +29063,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29254,7 +29269,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29332,7 +29347,7 @@
         <v>1.14</v>
       </c>
       <c r="AP137">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ137">
         <v>1.38</v>
@@ -29666,7 +29681,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29747,7 +29762,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ139">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR139">
         <v>1.21</v>
@@ -29872,7 +29887,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30078,7 +30093,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30774,7 +30789,7 @@
         <v>0.29</v>
       </c>
       <c r="AP144">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ144">
         <v>0.25</v>
@@ -30902,7 +30917,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -30983,7 +30998,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ145">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31108,7 +31123,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31932,7 +31947,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32216,7 +32231,7 @@
         <v>2.25</v>
       </c>
       <c r="AP151">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ151">
         <v>2</v>
@@ -32344,7 +32359,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32631,7 +32646,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ153">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.13</v>
@@ -32756,7 +32771,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -32913,6 +32928,830 @@
       </c>
       <c r="BP154">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7466211</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45668.52083333334</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>84</v>
+      </c>
+      <c r="H155" t="s">
+        <v>75</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <v>1</v>
+      </c>
+      <c r="N155">
+        <v>2</v>
+      </c>
+      <c r="O155" t="s">
+        <v>160</v>
+      </c>
+      <c r="P155" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q155">
+        <v>3.25</v>
+      </c>
+      <c r="R155">
+        <v>2.2</v>
+      </c>
+      <c r="S155">
+        <v>3.1</v>
+      </c>
+      <c r="T155">
+        <v>1.36</v>
+      </c>
+      <c r="U155">
+        <v>3</v>
+      </c>
+      <c r="V155">
+        <v>2.63</v>
+      </c>
+      <c r="W155">
+        <v>1.44</v>
+      </c>
+      <c r="X155">
+        <v>7</v>
+      </c>
+      <c r="Y155">
+        <v>1.1</v>
+      </c>
+      <c r="Z155">
+        <v>3.18</v>
+      </c>
+      <c r="AA155">
+        <v>3.48</v>
+      </c>
+      <c r="AB155">
+        <v>2.21</v>
+      </c>
+      <c r="AC155">
+        <v>1.04</v>
+      </c>
+      <c r="AD155">
+        <v>13</v>
+      </c>
+      <c r="AE155">
+        <v>1.26</v>
+      </c>
+      <c r="AF155">
+        <v>3.67</v>
+      </c>
+      <c r="AG155">
+        <v>1.9</v>
+      </c>
+      <c r="AH155">
+        <v>1.9</v>
+      </c>
+      <c r="AI155">
+        <v>1.62</v>
+      </c>
+      <c r="AJ155">
+        <v>2.2</v>
+      </c>
+      <c r="AK155">
+        <v>1.52</v>
+      </c>
+      <c r="AL155">
+        <v>1.29</v>
+      </c>
+      <c r="AM155">
+        <v>1.44</v>
+      </c>
+      <c r="AN155">
+        <v>1.25</v>
+      </c>
+      <c r="AO155">
+        <v>1</v>
+      </c>
+      <c r="AP155">
+        <v>1.22</v>
+      </c>
+      <c r="AQ155">
+        <v>1</v>
+      </c>
+      <c r="AR155">
+        <v>1.47</v>
+      </c>
+      <c r="AS155">
+        <v>1.29</v>
+      </c>
+      <c r="AT155">
+        <v>2.76</v>
+      </c>
+      <c r="AU155">
+        <v>4</v>
+      </c>
+      <c r="AV155">
+        <v>11</v>
+      </c>
+      <c r="AW155">
+        <v>6</v>
+      </c>
+      <c r="AX155">
+        <v>11</v>
+      </c>
+      <c r="AY155">
+        <v>11</v>
+      </c>
+      <c r="AZ155">
+        <v>24</v>
+      </c>
+      <c r="BA155">
+        <v>8</v>
+      </c>
+      <c r="BB155">
+        <v>4</v>
+      </c>
+      <c r="BC155">
+        <v>12</v>
+      </c>
+      <c r="BD155">
+        <v>2</v>
+      </c>
+      <c r="BE155">
+        <v>6.5</v>
+      </c>
+      <c r="BF155">
+        <v>1.96</v>
+      </c>
+      <c r="BG155">
+        <v>1.14</v>
+      </c>
+      <c r="BH155">
+        <v>4.6</v>
+      </c>
+      <c r="BI155">
+        <v>1.29</v>
+      </c>
+      <c r="BJ155">
+        <v>3.2</v>
+      </c>
+      <c r="BK155">
+        <v>1.49</v>
+      </c>
+      <c r="BL155">
+        <v>2.4</v>
+      </c>
+      <c r="BM155">
+        <v>1.78</v>
+      </c>
+      <c r="BN155">
+        <v>1.91</v>
+      </c>
+      <c r="BO155">
+        <v>2.2</v>
+      </c>
+      <c r="BP155">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7466206</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45668.61458333334</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>78</v>
+      </c>
+      <c r="H156" t="s">
+        <v>83</v>
+      </c>
+      <c r="I156">
+        <v>2</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>2</v>
+      </c>
+      <c r="L156">
+        <v>2</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>3</v>
+      </c>
+      <c r="O156" t="s">
+        <v>198</v>
+      </c>
+      <c r="P156" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q156">
+        <v>1.4</v>
+      </c>
+      <c r="R156">
+        <v>3.5</v>
+      </c>
+      <c r="S156">
+        <v>11</v>
+      </c>
+      <c r="T156">
+        <v>1.17</v>
+      </c>
+      <c r="U156">
+        <v>5</v>
+      </c>
+      <c r="V156">
+        <v>1.73</v>
+      </c>
+      <c r="W156">
+        <v>2</v>
+      </c>
+      <c r="X156">
+        <v>3.4</v>
+      </c>
+      <c r="Y156">
+        <v>1.3</v>
+      </c>
+      <c r="Z156">
+        <v>1.12</v>
+      </c>
+      <c r="AA156">
+        <v>9.5</v>
+      </c>
+      <c r="AB156">
+        <v>18.25</v>
+      </c>
+      <c r="AC156">
+        <v>0</v>
+      </c>
+      <c r="AD156">
+        <v>0</v>
+      </c>
+      <c r="AE156">
+        <v>1.04</v>
+      </c>
+      <c r="AF156">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AG156">
+        <v>1.22</v>
+      </c>
+      <c r="AH156">
+        <v>4</v>
+      </c>
+      <c r="AI156">
+        <v>1.91</v>
+      </c>
+      <c r="AJ156">
+        <v>1.91</v>
+      </c>
+      <c r="AK156">
+        <v>1.01</v>
+      </c>
+      <c r="AL156">
+        <v>1.06</v>
+      </c>
+      <c r="AM156">
+        <v>6</v>
+      </c>
+      <c r="AN156">
+        <v>2.75</v>
+      </c>
+      <c r="AO156">
+        <v>0.25</v>
+      </c>
+      <c r="AP156">
+        <v>2.78</v>
+      </c>
+      <c r="AQ156">
+        <v>0.22</v>
+      </c>
+      <c r="AR156">
+        <v>1.73</v>
+      </c>
+      <c r="AS156">
+        <v>0.95</v>
+      </c>
+      <c r="AT156">
+        <v>2.68</v>
+      </c>
+      <c r="AU156">
+        <v>7</v>
+      </c>
+      <c r="AV156">
+        <v>3</v>
+      </c>
+      <c r="AW156">
+        <v>13</v>
+      </c>
+      <c r="AX156">
+        <v>9</v>
+      </c>
+      <c r="AY156">
+        <v>25</v>
+      </c>
+      <c r="AZ156">
+        <v>17</v>
+      </c>
+      <c r="BA156">
+        <v>9</v>
+      </c>
+      <c r="BB156">
+        <v>1</v>
+      </c>
+      <c r="BC156">
+        <v>10</v>
+      </c>
+      <c r="BD156">
+        <v>1.05</v>
+      </c>
+      <c r="BE156">
+        <v>14</v>
+      </c>
+      <c r="BF156">
+        <v>11.5</v>
+      </c>
+      <c r="BG156">
+        <v>1.29</v>
+      </c>
+      <c r="BH156">
+        <v>3.15</v>
+      </c>
+      <c r="BI156">
+        <v>1.5</v>
+      </c>
+      <c r="BJ156">
+        <v>2.38</v>
+      </c>
+      <c r="BK156">
+        <v>1.8</v>
+      </c>
+      <c r="BL156">
+        <v>1.89</v>
+      </c>
+      <c r="BM156">
+        <v>2.23</v>
+      </c>
+      <c r="BN156">
+        <v>1.56</v>
+      </c>
+      <c r="BO156">
+        <v>2.8</v>
+      </c>
+      <c r="BP156">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7466213</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45668.66666666666</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>85</v>
+      </c>
+      <c r="H157" t="s">
+        <v>72</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>91</v>
+      </c>
+      <c r="P157" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q157">
+        <v>3.25</v>
+      </c>
+      <c r="R157">
+        <v>2.2</v>
+      </c>
+      <c r="S157">
+        <v>3.2</v>
+      </c>
+      <c r="T157">
+        <v>1.36</v>
+      </c>
+      <c r="U157">
+        <v>3</v>
+      </c>
+      <c r="V157">
+        <v>2.75</v>
+      </c>
+      <c r="W157">
+        <v>1.4</v>
+      </c>
+      <c r="X157">
+        <v>7</v>
+      </c>
+      <c r="Y157">
+        <v>1.1</v>
+      </c>
+      <c r="Z157">
+        <v>2.72</v>
+      </c>
+      <c r="AA157">
+        <v>3.38</v>
+      </c>
+      <c r="AB157">
+        <v>2.55</v>
+      </c>
+      <c r="AC157">
+        <v>1.05</v>
+      </c>
+      <c r="AD157">
+        <v>12</v>
+      </c>
+      <c r="AE157">
+        <v>1.26</v>
+      </c>
+      <c r="AF157">
+        <v>3.67</v>
+      </c>
+      <c r="AG157">
+        <v>1.84</v>
+      </c>
+      <c r="AH157">
+        <v>1.97</v>
+      </c>
+      <c r="AI157">
+        <v>1.67</v>
+      </c>
+      <c r="AJ157">
+        <v>2.1</v>
+      </c>
+      <c r="AK157">
+        <v>1.49</v>
+      </c>
+      <c r="AL157">
+        <v>1.3</v>
+      </c>
+      <c r="AM157">
+        <v>1.46</v>
+      </c>
+      <c r="AN157">
+        <v>1.5</v>
+      </c>
+      <c r="AO157">
+        <v>0.75</v>
+      </c>
+      <c r="AP157">
+        <v>1.33</v>
+      </c>
+      <c r="AQ157">
+        <v>1</v>
+      </c>
+      <c r="AR157">
+        <v>1.23</v>
+      </c>
+      <c r="AS157">
+        <v>1.26</v>
+      </c>
+      <c r="AT157">
+        <v>2.49</v>
+      </c>
+      <c r="AU157">
+        <v>4</v>
+      </c>
+      <c r="AV157">
+        <v>4</v>
+      </c>
+      <c r="AW157">
+        <v>5</v>
+      </c>
+      <c r="AX157">
+        <v>7</v>
+      </c>
+      <c r="AY157">
+        <v>11</v>
+      </c>
+      <c r="AZ157">
+        <v>12</v>
+      </c>
+      <c r="BA157">
+        <v>6</v>
+      </c>
+      <c r="BB157">
+        <v>4</v>
+      </c>
+      <c r="BC157">
+        <v>10</v>
+      </c>
+      <c r="BD157">
+        <v>1.97</v>
+      </c>
+      <c r="BE157">
+        <v>6.75</v>
+      </c>
+      <c r="BF157">
+        <v>2</v>
+      </c>
+      <c r="BG157">
+        <v>1.16</v>
+      </c>
+      <c r="BH157">
+        <v>4.4</v>
+      </c>
+      <c r="BI157">
+        <v>1.29</v>
+      </c>
+      <c r="BJ157">
+        <v>3.2</v>
+      </c>
+      <c r="BK157">
+        <v>1.49</v>
+      </c>
+      <c r="BL157">
+        <v>2.4</v>
+      </c>
+      <c r="BM157">
+        <v>1.77</v>
+      </c>
+      <c r="BN157">
+        <v>1.92</v>
+      </c>
+      <c r="BO157">
+        <v>2.18</v>
+      </c>
+      <c r="BP157">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7466214</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45668.70833333334</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>74</v>
+      </c>
+      <c r="H158" t="s">
+        <v>82</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158">
+        <v>2</v>
+      </c>
+      <c r="M158">
+        <v>2</v>
+      </c>
+      <c r="N158">
+        <v>4</v>
+      </c>
+      <c r="O158" t="s">
+        <v>199</v>
+      </c>
+      <c r="P158" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q158">
+        <v>1.83</v>
+      </c>
+      <c r="R158">
+        <v>2.75</v>
+      </c>
+      <c r="S158">
+        <v>6</v>
+      </c>
+      <c r="T158">
+        <v>1.22</v>
+      </c>
+      <c r="U158">
+        <v>4</v>
+      </c>
+      <c r="V158">
+        <v>2.1</v>
+      </c>
+      <c r="W158">
+        <v>1.67</v>
+      </c>
+      <c r="X158">
+        <v>4.5</v>
+      </c>
+      <c r="Y158">
+        <v>1.18</v>
+      </c>
+      <c r="Z158">
+        <v>1.44</v>
+      </c>
+      <c r="AA158">
+        <v>4.5</v>
+      </c>
+      <c r="AB158">
+        <v>6</v>
+      </c>
+      <c r="AC158">
+        <v>1.01</v>
+      </c>
+      <c r="AD158">
+        <v>17</v>
+      </c>
+      <c r="AE158">
+        <v>1.12</v>
+      </c>
+      <c r="AF158">
+        <v>5.87</v>
+      </c>
+      <c r="AG158">
+        <v>1.45</v>
+      </c>
+      <c r="AH158">
+        <v>2.63</v>
+      </c>
+      <c r="AI158">
+        <v>1.62</v>
+      </c>
+      <c r="AJ158">
+        <v>2.2</v>
+      </c>
+      <c r="AK158">
+        <v>1.11</v>
+      </c>
+      <c r="AL158">
+        <v>1.17</v>
+      </c>
+      <c r="AM158">
+        <v>2.75</v>
+      </c>
+      <c r="AN158">
+        <v>3</v>
+      </c>
+      <c r="AO158">
+        <v>2</v>
+      </c>
+      <c r="AP158">
+        <v>2.78</v>
+      </c>
+      <c r="AQ158">
+        <v>1.89</v>
+      </c>
+      <c r="AR158">
+        <v>2.37</v>
+      </c>
+      <c r="AS158">
+        <v>1.46</v>
+      </c>
+      <c r="AT158">
+        <v>3.83</v>
+      </c>
+      <c r="AU158">
+        <v>4</v>
+      </c>
+      <c r="AV158">
+        <v>6</v>
+      </c>
+      <c r="AW158">
+        <v>15</v>
+      </c>
+      <c r="AX158">
+        <v>4</v>
+      </c>
+      <c r="AY158">
+        <v>23</v>
+      </c>
+      <c r="AZ158">
+        <v>11</v>
+      </c>
+      <c r="BA158">
+        <v>11</v>
+      </c>
+      <c r="BB158">
+        <v>1</v>
+      </c>
+      <c r="BC158">
+        <v>12</v>
+      </c>
+      <c r="BD158">
+        <v>1.54</v>
+      </c>
+      <c r="BE158">
+        <v>6.75</v>
+      </c>
+      <c r="BF158">
+        <v>2.7</v>
+      </c>
+      <c r="BG158">
+        <v>1.19</v>
+      </c>
+      <c r="BH158">
+        <v>4</v>
+      </c>
+      <c r="BI158">
+        <v>1.35</v>
+      </c>
+      <c r="BJ158">
+        <v>2.9</v>
+      </c>
+      <c r="BK158">
+        <v>1.58</v>
+      </c>
+      <c r="BL158">
+        <v>2.2</v>
+      </c>
+      <c r="BM158">
+        <v>1.94</v>
+      </c>
+      <c r="BN158">
+        <v>1.76</v>
+      </c>
+      <c r="BO158">
+        <v>2.4</v>
+      </c>
+      <c r="BP158">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="278">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,9 @@
     <t>['68', '85']</t>
   </si>
   <si>
+    <t>['12', '36', '50', '68', '79', '90+1']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -842,6 +845,9 @@
   </si>
   <si>
     <t>['41', '74']</t>
+  </si>
+  <si>
+    <t>['31', '40']</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1746,7 +1752,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ3">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1871,7 +1877,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2077,7 +2083,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2283,7 +2289,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2901,7 +2907,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3803,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4137,7 +4143,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4343,7 +4349,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4549,7 +4555,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5373,7 +5379,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5579,7 +5585,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -6072,7 +6078,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
         <v>0.78</v>
@@ -6197,7 +6203,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6609,7 +6615,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7021,7 +7027,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7433,7 +7439,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7639,7 +7645,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8541,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ36">
         <v>0.5600000000000001</v>
@@ -8669,7 +8675,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9081,7 +9087,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9287,7 +9293,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9983,7 +9989,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ43">
         <v>0.33</v>
@@ -10317,7 +10323,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10523,7 +10529,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10604,7 +10610,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ46">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR46">
         <v>1.08</v>
@@ -10729,7 +10735,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10935,7 +10941,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11141,7 +11147,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11347,7 +11353,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11553,7 +11559,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11965,7 +11971,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12171,7 +12177,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12377,7 +12383,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12583,7 +12589,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13279,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ59">
         <v>0.78</v>
@@ -13613,7 +13619,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13819,7 +13825,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14106,7 +14112,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ63">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR63">
         <v>1.02</v>
@@ -14643,7 +14649,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14849,7 +14855,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15467,7 +15473,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15879,7 +15885,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16085,7 +16091,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16497,7 +16503,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16703,7 +16709,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17115,7 +17121,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17321,7 +17327,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17527,7 +17533,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18351,7 +18357,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18763,7 +18769,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19047,7 +19053,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ87">
         <v>0.5</v>
@@ -19256,7 +19262,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ88">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19381,7 +19387,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19587,7 +19593,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19793,7 +19799,7 @@
         <v>91</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q91">
         <v>5.5</v>
@@ -20205,7 +20211,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20411,7 +20417,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20823,7 +20829,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21235,7 +21241,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -22265,7 +22271,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22471,7 +22477,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22677,7 +22683,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22883,7 +22889,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -22961,7 +22967,7 @@
         <v>2</v>
       </c>
       <c r="AP106">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ106">
         <v>1.89</v>
@@ -23295,7 +23301,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23376,7 +23382,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ108">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR108">
         <v>1.94</v>
@@ -23913,7 +23919,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24325,7 +24331,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24531,7 +24537,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24737,7 +24743,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24943,7 +24949,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25848,7 +25854,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR120">
         <v>1.14</v>
@@ -26385,7 +26391,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26591,7 +26597,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26669,7 +26675,7 @@
         <v>1.17</v>
       </c>
       <c r="AP124">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ124">
         <v>1.22</v>
@@ -27003,7 +27009,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27209,7 +27215,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27827,7 +27833,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28033,7 +28039,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28239,7 +28245,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28651,7 +28657,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -29063,7 +29069,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29269,7 +29275,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29350,7 +29356,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ137">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR137">
         <v>1.19</v>
@@ -29681,7 +29687,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29887,7 +29893,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30093,7 +30099,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30583,7 +30589,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ143">
         <v>0.5</v>
@@ -30917,7 +30923,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31123,7 +31129,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31947,7 +31953,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32359,7 +32365,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32771,7 +32777,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -32977,7 +32983,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33389,7 +33395,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33595,7 +33601,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33752,6 +33758,212 @@
       </c>
       <c r="BP158">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7466208</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45669.34375</v>
+      </c>
+      <c r="F159">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>81</v>
+      </c>
+      <c r="H159" t="s">
+        <v>86</v>
+      </c>
+      <c r="I159">
+        <v>2</v>
+      </c>
+      <c r="J159">
+        <v>2</v>
+      </c>
+      <c r="K159">
+        <v>4</v>
+      </c>
+      <c r="L159">
+        <v>6</v>
+      </c>
+      <c r="M159">
+        <v>2</v>
+      </c>
+      <c r="N159">
+        <v>8</v>
+      </c>
+      <c r="O159" t="s">
+        <v>200</v>
+      </c>
+      <c r="P159" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q159">
+        <v>2</v>
+      </c>
+      <c r="R159">
+        <v>2.4</v>
+      </c>
+      <c r="S159">
+        <v>6.5</v>
+      </c>
+      <c r="T159">
+        <v>1.33</v>
+      </c>
+      <c r="U159">
+        <v>3.25</v>
+      </c>
+      <c r="V159">
+        <v>2.63</v>
+      </c>
+      <c r="W159">
+        <v>1.44</v>
+      </c>
+      <c r="X159">
+        <v>6.5</v>
+      </c>
+      <c r="Y159">
+        <v>1.11</v>
+      </c>
+      <c r="Z159">
+        <v>1.44</v>
+      </c>
+      <c r="AA159">
+        <v>4.4</v>
+      </c>
+      <c r="AB159">
+        <v>6</v>
+      </c>
+      <c r="AC159">
+        <v>1.03</v>
+      </c>
+      <c r="AD159">
+        <v>15</v>
+      </c>
+      <c r="AE159">
+        <v>1.19</v>
+      </c>
+      <c r="AF159">
+        <v>4.45</v>
+      </c>
+      <c r="AG159">
+        <v>1.65</v>
+      </c>
+      <c r="AH159">
+        <v>2.1</v>
+      </c>
+      <c r="AI159">
+        <v>1.91</v>
+      </c>
+      <c r="AJ159">
+        <v>1.91</v>
+      </c>
+      <c r="AK159">
+        <v>1.1</v>
+      </c>
+      <c r="AL159">
+        <v>1.18</v>
+      </c>
+      <c r="AM159">
+        <v>2.85</v>
+      </c>
+      <c r="AN159">
+        <v>2.25</v>
+      </c>
+      <c r="AO159">
+        <v>1.38</v>
+      </c>
+      <c r="AP159">
+        <v>2.33</v>
+      </c>
+      <c r="AQ159">
+        <v>1.22</v>
+      </c>
+      <c r="AR159">
+        <v>1.99</v>
+      </c>
+      <c r="AS159">
+        <v>0.83</v>
+      </c>
+      <c r="AT159">
+        <v>2.82</v>
+      </c>
+      <c r="AU159">
+        <v>13</v>
+      </c>
+      <c r="AV159">
+        <v>4</v>
+      </c>
+      <c r="AW159">
+        <v>10</v>
+      </c>
+      <c r="AX159">
+        <v>4</v>
+      </c>
+      <c r="AY159">
+        <v>27</v>
+      </c>
+      <c r="AZ159">
+        <v>10</v>
+      </c>
+      <c r="BA159">
+        <v>7</v>
+      </c>
+      <c r="BB159">
+        <v>4</v>
+      </c>
+      <c r="BC159">
+        <v>11</v>
+      </c>
+      <c r="BD159">
+        <v>1.26</v>
+      </c>
+      <c r="BE159">
+        <v>8</v>
+      </c>
+      <c r="BF159">
+        <v>4.1</v>
+      </c>
+      <c r="BG159">
+        <v>1.21</v>
+      </c>
+      <c r="BH159">
+        <v>3.8</v>
+      </c>
+      <c r="BI159">
+        <v>1.38</v>
+      </c>
+      <c r="BJ159">
+        <v>2.7</v>
+      </c>
+      <c r="BK159">
+        <v>1.64</v>
+      </c>
+      <c r="BL159">
+        <v>2.1</v>
+      </c>
+      <c r="BM159">
+        <v>1.98</v>
+      </c>
+      <c r="BN159">
+        <v>1.72</v>
+      </c>
+      <c r="BO159">
+        <v>2.48</v>
+      </c>
+      <c r="BP159">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,9 @@
     <t>['12', '36', '50', '68', '79', '90+1']</t>
   </si>
   <si>
+    <t>['19', '75']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -848,6 +851,12 @@
   </si>
   <si>
     <t>['31', '40']</t>
+  </si>
+  <si>
+    <t>['60', '65']</t>
+  </si>
+  <si>
+    <t>['7', '13', '28', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1543,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ2">
         <v>0.78</v>
@@ -1749,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ3">
         <v>1.22</v>
@@ -1877,7 +1886,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2083,7 +2092,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2289,7 +2298,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2907,7 +2916,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3194,7 +3203,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ10">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3400,7 +3409,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3606,7 +3615,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ12">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4143,7 +4152,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4349,7 +4358,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4555,7 +4564,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5045,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
         <v>1.89</v>
@@ -5379,7 +5388,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5585,7 +5594,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5663,10 +5672,10 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
@@ -5869,7 +5878,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ23">
         <v>1.89</v>
@@ -6203,7 +6212,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6615,7 +6624,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7027,7 +7036,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7439,7 +7448,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7645,7 +7654,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8675,7 +8684,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8753,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ37">
         <v>2</v>
@@ -8959,7 +8968,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
         <v>1.11</v>
@@ -9087,7 +9096,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9168,7 +9177,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ39">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR39">
         <v>1.82</v>
@@ -9293,7 +9302,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9786,7 +9795,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ42">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR42">
         <v>1.23</v>
@@ -9992,7 +10001,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR43">
         <v>2.19</v>
@@ -10323,7 +10332,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10529,7 +10538,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10735,7 +10744,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10941,7 +10950,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11147,7 +11156,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11353,7 +11362,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11559,7 +11568,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11843,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ52">
         <v>0.78</v>
@@ -11971,7 +11980,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12177,7 +12186,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12258,7 +12267,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ54">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR54">
         <v>1.37</v>
@@ -12383,7 +12392,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12589,7 +12598,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13082,7 +13091,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR58">
         <v>1.08</v>
@@ -13491,7 +13500,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ60">
         <v>1.22</v>
@@ -13619,7 +13628,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13825,7 +13834,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -13906,7 +13915,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ62">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR62">
         <v>2.58</v>
@@ -14315,7 +14324,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14649,7 +14658,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14855,7 +14864,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15139,7 +15148,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ68">
         <v>1.44</v>
@@ -15473,7 +15482,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15885,7 +15894,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15966,7 +15975,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ72">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16091,7 +16100,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16378,7 +16387,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ74">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR74">
         <v>1.44</v>
@@ -16503,7 +16512,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16709,7 +16718,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17121,7 +17130,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17199,10 +17208,10 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ78">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR78">
         <v>1.07</v>
@@ -17327,7 +17336,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17533,7 +17542,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18357,7 +18366,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18435,7 +18444,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>0.22</v>
@@ -18769,7 +18778,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19387,7 +19396,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19593,7 +19602,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19671,7 +19680,7 @@
         <v>1.75</v>
       </c>
       <c r="AP90">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ90">
         <v>1.89</v>
@@ -19799,7 +19808,7 @@
         <v>91</v>
       </c>
       <c r="P91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q91">
         <v>5.5</v>
@@ -20211,7 +20220,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20417,7 +20426,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20495,7 +20504,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ94">
         <v>1.89</v>
@@ -20704,7 +20713,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR95">
         <v>1.29</v>
@@ -20829,7 +20838,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21241,7 +21250,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21322,7 +21331,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ98">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR98">
         <v>1.7</v>
@@ -21528,7 +21537,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ99">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21937,7 +21946,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22271,7 +22280,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22349,7 +22358,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
         <v>2.33</v>
@@ -22477,7 +22486,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22683,7 +22692,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22889,7 +22898,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23301,7 +23310,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23588,7 +23597,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ109">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23791,10 +23800,10 @@
         <v>0</v>
       </c>
       <c r="AP110">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ110">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR110">
         <v>1.62</v>
@@ -23919,7 +23928,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24331,7 +24340,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24537,7 +24546,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24618,7 +24627,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ114">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -24743,7 +24752,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24949,7 +24958,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25645,10 +25654,10 @@
         <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ119">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR119">
         <v>1.34</v>
@@ -25851,7 +25860,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ120">
         <v>1.22</v>
@@ -26057,7 +26066,7 @@
         <v>0.83</v>
       </c>
       <c r="AP121">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ121">
         <v>1.11</v>
@@ -26391,7 +26400,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26597,7 +26606,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27009,7 +27018,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27215,7 +27224,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27296,7 +27305,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ127">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR127">
         <v>1.82</v>
@@ -27833,7 +27842,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28039,7 +28048,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28245,7 +28254,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28529,7 +28538,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ133">
         <v>0.5600000000000001</v>
@@ -28657,7 +28666,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28738,7 +28747,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ134">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR134">
         <v>1.12</v>
@@ -29069,7 +29078,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29150,7 +29159,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ136">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29275,7 +29284,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29687,7 +29696,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29893,7 +29902,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -29971,7 +29980,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AQ140">
         <v>0.5</v>
@@ -30099,7 +30108,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30798,7 +30807,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ144">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR144">
         <v>1.74</v>
@@ -30923,7 +30932,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31001,7 +31010,7 @@
         <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145">
         <v>1.89</v>
@@ -31129,7 +31138,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31622,7 +31631,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ148">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AR148">
         <v>1.21</v>
@@ -31953,7 +31962,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32365,7 +32374,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32777,7 +32786,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -32983,7 +32992,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33395,7 +33404,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33601,7 +33610,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33807,7 +33816,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -33964,6 +33973,624 @@
       </c>
       <c r="BP159">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7466207</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45669.4375</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>70</v>
+      </c>
+      <c r="H160" t="s">
+        <v>73</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160" t="s">
+        <v>91</v>
+      </c>
+      <c r="P160" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q160">
+        <v>2.4</v>
+      </c>
+      <c r="R160">
+        <v>2.1</v>
+      </c>
+      <c r="S160">
+        <v>5</v>
+      </c>
+      <c r="T160">
+        <v>1.44</v>
+      </c>
+      <c r="U160">
+        <v>2.63</v>
+      </c>
+      <c r="V160">
+        <v>3.25</v>
+      </c>
+      <c r="W160">
+        <v>1.33</v>
+      </c>
+      <c r="X160">
+        <v>9</v>
+      </c>
+      <c r="Y160">
+        <v>1.07</v>
+      </c>
+      <c r="Z160">
+        <v>1.73</v>
+      </c>
+      <c r="AA160">
+        <v>3.6</v>
+      </c>
+      <c r="AB160">
+        <v>4.4</v>
+      </c>
+      <c r="AC160">
+        <v>1.04</v>
+      </c>
+      <c r="AD160">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE160">
+        <v>1.33</v>
+      </c>
+      <c r="AF160">
+        <v>3.19</v>
+      </c>
+      <c r="AG160">
+        <v>1.95</v>
+      </c>
+      <c r="AH160">
+        <v>1.75</v>
+      </c>
+      <c r="AI160">
+        <v>1.95</v>
+      </c>
+      <c r="AJ160">
+        <v>1.8</v>
+      </c>
+      <c r="AK160">
+        <v>1.2</v>
+      </c>
+      <c r="AL160">
+        <v>1.28</v>
+      </c>
+      <c r="AM160">
+        <v>1.95</v>
+      </c>
+      <c r="AN160">
+        <v>1.5</v>
+      </c>
+      <c r="AO160">
+        <v>0.25</v>
+      </c>
+      <c r="AP160">
+        <v>1.44</v>
+      </c>
+      <c r="AQ160">
+        <v>0.33</v>
+      </c>
+      <c r="AR160">
+        <v>1.27</v>
+      </c>
+      <c r="AS160">
+        <v>1.09</v>
+      </c>
+      <c r="AT160">
+        <v>2.36</v>
+      </c>
+      <c r="AU160">
+        <v>6</v>
+      </c>
+      <c r="AV160">
+        <v>2</v>
+      </c>
+      <c r="AW160">
+        <v>11</v>
+      </c>
+      <c r="AX160">
+        <v>4</v>
+      </c>
+      <c r="AY160">
+        <v>20</v>
+      </c>
+      <c r="AZ160">
+        <v>8</v>
+      </c>
+      <c r="BA160">
+        <v>15</v>
+      </c>
+      <c r="BB160">
+        <v>2</v>
+      </c>
+      <c r="BC160">
+        <v>17</v>
+      </c>
+      <c r="BD160">
+        <v>1.46</v>
+      </c>
+      <c r="BE160">
+        <v>7</v>
+      </c>
+      <c r="BF160">
+        <v>2.95</v>
+      </c>
+      <c r="BG160">
+        <v>1.24</v>
+      </c>
+      <c r="BH160">
+        <v>3.55</v>
+      </c>
+      <c r="BI160">
+        <v>1.43</v>
+      </c>
+      <c r="BJ160">
+        <v>2.55</v>
+      </c>
+      <c r="BK160">
+        <v>1.7</v>
+      </c>
+      <c r="BL160">
+        <v>2</v>
+      </c>
+      <c r="BM160">
+        <v>2.05</v>
+      </c>
+      <c r="BN160">
+        <v>1.66</v>
+      </c>
+      <c r="BO160">
+        <v>2.55</v>
+      </c>
+      <c r="BP160">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7466209</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45669.4375</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>71</v>
+      </c>
+      <c r="H161" t="s">
+        <v>76</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>2</v>
+      </c>
+      <c r="N161">
+        <v>3</v>
+      </c>
+      <c r="O161" t="s">
+        <v>134</v>
+      </c>
+      <c r="P161" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q161">
+        <v>2</v>
+      </c>
+      <c r="R161">
+        <v>2.5</v>
+      </c>
+      <c r="S161">
+        <v>5.5</v>
+      </c>
+      <c r="T161">
+        <v>1.29</v>
+      </c>
+      <c r="U161">
+        <v>3.5</v>
+      </c>
+      <c r="V161">
+        <v>2.25</v>
+      </c>
+      <c r="W161">
+        <v>1.57</v>
+      </c>
+      <c r="X161">
+        <v>5.5</v>
+      </c>
+      <c r="Y161">
+        <v>1.14</v>
+      </c>
+      <c r="Z161">
+        <v>1.55</v>
+      </c>
+      <c r="AA161">
+        <v>4.33</v>
+      </c>
+      <c r="AB161">
+        <v>4.75</v>
+      </c>
+      <c r="AC161">
+        <v>1.02</v>
+      </c>
+      <c r="AD161">
+        <v>17</v>
+      </c>
+      <c r="AE161">
+        <v>1.16</v>
+      </c>
+      <c r="AF161">
+        <v>4.93</v>
+      </c>
+      <c r="AG161">
+        <v>1.53</v>
+      </c>
+      <c r="AH161">
+        <v>2.35</v>
+      </c>
+      <c r="AI161">
+        <v>1.67</v>
+      </c>
+      <c r="AJ161">
+        <v>2.1</v>
+      </c>
+      <c r="AK161">
+        <v>1.14</v>
+      </c>
+      <c r="AL161">
+        <v>1.2</v>
+      </c>
+      <c r="AM161">
+        <v>2.45</v>
+      </c>
+      <c r="AN161">
+        <v>2.13</v>
+      </c>
+      <c r="AO161">
+        <v>2.5</v>
+      </c>
+      <c r="AP161">
+        <v>1.89</v>
+      </c>
+      <c r="AQ161">
+        <v>2.56</v>
+      </c>
+      <c r="AR161">
+        <v>1.8</v>
+      </c>
+      <c r="AS161">
+        <v>1.26</v>
+      </c>
+      <c r="AT161">
+        <v>3.06</v>
+      </c>
+      <c r="AU161">
+        <v>5</v>
+      </c>
+      <c r="AV161">
+        <v>4</v>
+      </c>
+      <c r="AW161">
+        <v>13</v>
+      </c>
+      <c r="AX161">
+        <v>6</v>
+      </c>
+      <c r="AY161">
+        <v>21</v>
+      </c>
+      <c r="AZ161">
+        <v>10</v>
+      </c>
+      <c r="BA161">
+        <v>9</v>
+      </c>
+      <c r="BB161">
+        <v>2</v>
+      </c>
+      <c r="BC161">
+        <v>11</v>
+      </c>
+      <c r="BD161">
+        <v>1.35</v>
+      </c>
+      <c r="BE161">
+        <v>7</v>
+      </c>
+      <c r="BF161">
+        <v>3.55</v>
+      </c>
+      <c r="BG161">
+        <v>1.21</v>
+      </c>
+      <c r="BH161">
+        <v>3.8</v>
+      </c>
+      <c r="BI161">
+        <v>1.38</v>
+      </c>
+      <c r="BJ161">
+        <v>2.75</v>
+      </c>
+      <c r="BK161">
+        <v>1.63</v>
+      </c>
+      <c r="BL161">
+        <v>2.12</v>
+      </c>
+      <c r="BM161">
+        <v>1.96</v>
+      </c>
+      <c r="BN161">
+        <v>1.73</v>
+      </c>
+      <c r="BO161">
+        <v>2.43</v>
+      </c>
+      <c r="BP161">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7466212</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45669.53125</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>87</v>
+      </c>
+      <c r="H162" t="s">
+        <v>80</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>3</v>
+      </c>
+      <c r="K162">
+        <v>4</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>4</v>
+      </c>
+      <c r="N162">
+        <v>6</v>
+      </c>
+      <c r="O162" t="s">
+        <v>201</v>
+      </c>
+      <c r="P162" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q162">
+        <v>2.75</v>
+      </c>
+      <c r="R162">
+        <v>2.2</v>
+      </c>
+      <c r="S162">
+        <v>3.75</v>
+      </c>
+      <c r="T162">
+        <v>1.36</v>
+      </c>
+      <c r="U162">
+        <v>3</v>
+      </c>
+      <c r="V162">
+        <v>2.75</v>
+      </c>
+      <c r="W162">
+        <v>1.4</v>
+      </c>
+      <c r="X162">
+        <v>7</v>
+      </c>
+      <c r="Y162">
+        <v>1.1</v>
+      </c>
+      <c r="Z162">
+        <v>2.15</v>
+      </c>
+      <c r="AA162">
+        <v>3.4</v>
+      </c>
+      <c r="AB162">
+        <v>3</v>
+      </c>
+      <c r="AC162">
+        <v>1.04</v>
+      </c>
+      <c r="AD162">
+        <v>13</v>
+      </c>
+      <c r="AE162">
+        <v>1.26</v>
+      </c>
+      <c r="AF162">
+        <v>3.67</v>
+      </c>
+      <c r="AG162">
+        <v>1.8</v>
+      </c>
+      <c r="AH162">
+        <v>1.91</v>
+      </c>
+      <c r="AI162">
+        <v>1.67</v>
+      </c>
+      <c r="AJ162">
+        <v>2.1</v>
+      </c>
+      <c r="AK162">
+        <v>1.36</v>
+      </c>
+      <c r="AL162">
+        <v>1.29</v>
+      </c>
+      <c r="AM162">
+        <v>1.62</v>
+      </c>
+      <c r="AN162">
+        <v>1.88</v>
+      </c>
+      <c r="AO162">
+        <v>0.33</v>
+      </c>
+      <c r="AP162">
+        <v>1.67</v>
+      </c>
+      <c r="AQ162">
+        <v>0.6</v>
+      </c>
+      <c r="AR162">
+        <v>1.26</v>
+      </c>
+      <c r="AS162">
+        <v>1.25</v>
+      </c>
+      <c r="AT162">
+        <v>2.51</v>
+      </c>
+      <c r="AU162">
+        <v>8</v>
+      </c>
+      <c r="AV162">
+        <v>7</v>
+      </c>
+      <c r="AW162">
+        <v>9</v>
+      </c>
+      <c r="AX162">
+        <v>7</v>
+      </c>
+      <c r="AY162">
+        <v>23</v>
+      </c>
+      <c r="AZ162">
+        <v>20</v>
+      </c>
+      <c r="BA162">
+        <v>7</v>
+      </c>
+      <c r="BB162">
+        <v>4</v>
+      </c>
+      <c r="BC162">
+        <v>11</v>
+      </c>
+      <c r="BD162">
+        <v>1.94</v>
+      </c>
+      <c r="BE162">
+        <v>6.4</v>
+      </c>
+      <c r="BF162">
+        <v>2.07</v>
+      </c>
+      <c r="BG162">
+        <v>1.29</v>
+      </c>
+      <c r="BH162">
+        <v>3.15</v>
+      </c>
+      <c r="BI162">
+        <v>1.5</v>
+      </c>
+      <c r="BJ162">
+        <v>2.33</v>
+      </c>
+      <c r="BK162">
+        <v>1.84</v>
+      </c>
+      <c r="BL162">
+        <v>1.84</v>
+      </c>
+      <c r="BM162">
+        <v>2.3</v>
+      </c>
+      <c r="BN162">
+        <v>1.53</v>
+      </c>
+      <c r="BO162">
+        <v>2.95</v>
+      </c>
+      <c r="BP162">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="284">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -622,6 +622,12 @@
     <t>['19', '75']</t>
   </si>
   <si>
+    <t>['2', '38', '90+4']</t>
+  </si>
+  <si>
+    <t>['5', '90+1']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -857,6 +863,9 @@
   </si>
   <si>
     <t>['7', '13', '28', '90+5']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP166"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1886,7 +1895,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2092,7 +2101,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2173,7 +2182,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ5">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2298,7 +2307,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2788,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ8">
         <v>0.5600000000000001</v>
@@ -2916,7 +2925,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -2994,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>1.11</v>
@@ -4152,7 +4161,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4233,7 +4242,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4358,7 +4367,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4439,7 +4448,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ16">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4564,7 +4573,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -4642,10 +4651,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4848,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
         <v>1.22</v>
@@ -5388,7 +5397,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5469,7 +5478,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ21">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR21">
         <v>0.96</v>
@@ -5594,7 +5603,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5881,7 +5890,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ23">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR23">
         <v>1.65</v>
@@ -6212,7 +6221,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6293,7 +6302,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR25">
         <v>1.08</v>
@@ -6496,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>0.22</v>
@@ -6624,7 +6633,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6705,7 +6714,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ27">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR27">
         <v>1.81</v>
@@ -6911,7 +6920,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR28">
         <v>0.73</v>
@@ -7036,7 +7045,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7448,7 +7457,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7526,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7654,7 +7663,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7732,7 +7741,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ32">
         <v>1.44</v>
@@ -7938,7 +7947,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33">
         <v>0.5</v>
@@ -8684,7 +8693,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8765,7 +8774,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ37">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR37">
         <v>1.07</v>
@@ -9096,7 +9105,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9302,7 +9311,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9586,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
         <v>0.22</v>
@@ -10332,7 +10341,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10410,10 +10419,10 @@
         <v>2.33</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR45">
         <v>1.06</v>
@@ -10538,7 +10547,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10616,7 +10625,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ46">
         <v>1.22</v>
@@ -10744,7 +10753,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10950,7 +10959,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11028,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>1.89</v>
@@ -11156,7 +11165,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11362,7 +11371,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11443,7 +11452,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ50">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11568,7 +11577,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11980,7 +11989,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12061,7 +12070,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12186,7 +12195,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12392,7 +12401,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12470,10 +12479,10 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ55">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR55">
         <v>1.25</v>
@@ -12598,7 +12607,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12679,7 +12688,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ56">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR56">
         <v>1.55</v>
@@ -13088,7 +13097,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.33</v>
@@ -13628,7 +13637,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13834,7 +13843,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14658,7 +14667,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14736,7 +14745,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ66">
         <v>0.22</v>
@@ -14864,7 +14873,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -14942,7 +14951,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.5</v>
@@ -15482,7 +15491,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15563,7 +15572,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ70">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR70">
         <v>2.32</v>
@@ -15769,7 +15778,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ71">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR71">
         <v>1.43</v>
@@ -15894,7 +15903,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16100,7 +16109,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16181,7 +16190,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ73">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR73">
         <v>2.44</v>
@@ -16512,7 +16521,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16718,7 +16727,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -16796,10 +16805,10 @@
         <v>1.5</v>
       </c>
       <c r="AP76">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR76">
         <v>1.77</v>
@@ -17002,7 +17011,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77">
         <v>1.11</v>
@@ -17130,7 +17139,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17336,7 +17345,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17542,7 +17551,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17620,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ80">
         <v>0.78</v>
@@ -18035,7 +18044,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ82">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR82">
         <v>1.34</v>
@@ -18366,7 +18375,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18778,7 +18787,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18856,10 +18865,10 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ86">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19396,7 +19405,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19602,7 +19611,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19808,7 +19817,7 @@
         <v>91</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>5.5</v>
@@ -19886,7 +19895,7 @@
         <v>1.4</v>
       </c>
       <c r="AP91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ91">
         <v>1.44</v>
@@ -20220,7 +20229,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20301,7 +20310,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ93">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR93">
         <v>2.04</v>
@@ -20426,7 +20435,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20507,7 +20516,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ94">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR94">
         <v>1.67</v>
@@ -20838,7 +20847,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -20916,7 +20925,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>0.5600000000000001</v>
@@ -21125,7 +21134,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ97">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR97">
         <v>1.38</v>
@@ -21250,7 +21259,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21740,7 +21749,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ100">
         <v>0.5</v>
@@ -22152,7 +22161,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>1.11</v>
@@ -22280,7 +22289,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22361,7 +22370,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ103">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR103">
         <v>1.38</v>
@@ -22486,7 +22495,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22692,7 +22701,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22773,7 +22782,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ105">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR105">
         <v>1.24</v>
@@ -22898,7 +22907,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -23310,7 +23319,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23594,7 +23603,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>0.33</v>
@@ -23928,7 +23937,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24215,7 +24224,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ112">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR112">
         <v>2.46</v>
@@ -24340,7 +24349,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24546,7 +24555,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24752,7 +24761,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24833,7 +24842,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ115">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -24958,7 +24967,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25036,7 +25045,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ116">
         <v>0.78</v>
@@ -26272,7 +26281,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -26400,7 +26409,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26478,10 +26487,10 @@
         <v>2.57</v>
       </c>
       <c r="AP123">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ123">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR123">
         <v>1.43</v>
@@ -26606,7 +26615,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -27018,7 +27027,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27224,7 +27233,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27714,7 +27723,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -27842,7 +27851,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -28048,7 +28057,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28129,7 +28138,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ131">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28254,7 +28263,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28666,7 +28675,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28744,7 +28753,7 @@
         <v>0</v>
       </c>
       <c r="AP134">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ134">
         <v>0.6</v>
@@ -29078,7 +29087,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29284,7 +29293,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29362,7 +29371,7 @@
         <v>1.14</v>
       </c>
       <c r="AP137">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ137">
         <v>1.22</v>
@@ -29571,7 +29580,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ138">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AR138">
         <v>1.59</v>
@@ -29696,7 +29705,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29902,7 +29911,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -30108,7 +30117,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30186,7 +30195,7 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ141">
         <v>1.22</v>
@@ -30601,7 +30610,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ143">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR143">
         <v>2.08</v>
@@ -30932,7 +30941,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31013,7 +31022,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ145">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR145">
         <v>1.32</v>
@@ -31138,7 +31147,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31422,7 +31431,7 @@
         <v>0.88</v>
       </c>
       <c r="AP147">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ147">
         <v>0.78</v>
@@ -31962,7 +31971,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32249,7 +32258,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ151">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR151">
         <v>2.48</v>
@@ -32374,7 +32383,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32452,7 +32461,7 @@
         <v>0.88</v>
       </c>
       <c r="AP152">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ152">
         <v>1.11</v>
@@ -32658,7 +32667,7 @@
         <v>0.86</v>
       </c>
       <c r="AP153">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -32786,7 +32795,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -32992,7 +33001,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33404,7 +33413,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33482,7 +33491,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -33610,7 +33619,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33691,7 +33700,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ158">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AR158">
         <v>2.37</v>
@@ -33816,7 +33825,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34228,7 +34237,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34434,7 +34443,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34591,6 +34600,830 @@
       </c>
       <c r="BP162">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7466220</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45675.52083333334</v>
+      </c>
+      <c r="F163">
+        <v>19</v>
+      </c>
+      <c r="G163" t="s">
+        <v>85</v>
+      </c>
+      <c r="H163" t="s">
+        <v>74</v>
+      </c>
+      <c r="I163">
+        <v>2</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>3</v>
+      </c>
+      <c r="L163">
+        <v>3</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>4</v>
+      </c>
+      <c r="O163" t="s">
+        <v>202</v>
+      </c>
+      <c r="P163" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q163">
+        <v>8</v>
+      </c>
+      <c r="R163">
+        <v>3</v>
+      </c>
+      <c r="S163">
+        <v>1.62</v>
+      </c>
+      <c r="T163">
+        <v>1.2</v>
+      </c>
+      <c r="U163">
+        <v>4.33</v>
+      </c>
+      <c r="V163">
+        <v>1.91</v>
+      </c>
+      <c r="W163">
+        <v>1.8</v>
+      </c>
+      <c r="X163">
+        <v>4</v>
+      </c>
+      <c r="Y163">
+        <v>1.22</v>
+      </c>
+      <c r="Z163">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA163">
+        <v>5.8</v>
+      </c>
+      <c r="AB163">
+        <v>1.23</v>
+      </c>
+      <c r="AC163">
+        <v>0</v>
+      </c>
+      <c r="AD163">
+        <v>0</v>
+      </c>
+      <c r="AE163">
+        <v>1.09</v>
+      </c>
+      <c r="AF163">
+        <v>7</v>
+      </c>
+      <c r="AG163">
+        <v>1.32</v>
+      </c>
+      <c r="AH163">
+        <v>3.21</v>
+      </c>
+      <c r="AI163">
+        <v>1.7</v>
+      </c>
+      <c r="AJ163">
+        <v>2.05</v>
+      </c>
+      <c r="AK163">
+        <v>3.9</v>
+      </c>
+      <c r="AL163">
+        <v>1.11</v>
+      </c>
+      <c r="AM163">
+        <v>1.06</v>
+      </c>
+      <c r="AN163">
+        <v>1.33</v>
+      </c>
+      <c r="AO163">
+        <v>2.33</v>
+      </c>
+      <c r="AP163">
+        <v>1.5</v>
+      </c>
+      <c r="AQ163">
+        <v>2.1</v>
+      </c>
+      <c r="AR163">
+        <v>1.24</v>
+      </c>
+      <c r="AS163">
+        <v>1.82</v>
+      </c>
+      <c r="AT163">
+        <v>3.06</v>
+      </c>
+      <c r="AU163">
+        <v>5</v>
+      </c>
+      <c r="AV163">
+        <v>5</v>
+      </c>
+      <c r="AW163">
+        <v>4</v>
+      </c>
+      <c r="AX163">
+        <v>14</v>
+      </c>
+      <c r="AY163">
+        <v>9</v>
+      </c>
+      <c r="AZ163">
+        <v>23</v>
+      </c>
+      <c r="BA163">
+        <v>3</v>
+      </c>
+      <c r="BB163">
+        <v>5</v>
+      </c>
+      <c r="BC163">
+        <v>8</v>
+      </c>
+      <c r="BD163">
+        <v>5.4</v>
+      </c>
+      <c r="BE163">
+        <v>10</v>
+      </c>
+      <c r="BF163">
+        <v>1.15</v>
+      </c>
+      <c r="BG163">
+        <v>1.12</v>
+      </c>
+      <c r="BH163">
+        <v>5.1</v>
+      </c>
+      <c r="BI163">
+        <v>1.23</v>
+      </c>
+      <c r="BJ163">
+        <v>3.65</v>
+      </c>
+      <c r="BK163">
+        <v>1.38</v>
+      </c>
+      <c r="BL163">
+        <v>2.7</v>
+      </c>
+      <c r="BM163">
+        <v>1.61</v>
+      </c>
+      <c r="BN163">
+        <v>2.15</v>
+      </c>
+      <c r="BO163">
+        <v>1.95</v>
+      </c>
+      <c r="BP163">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7466216</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45675.61458333334</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>76</v>
+      </c>
+      <c r="H164" t="s">
+        <v>82</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164" t="s">
+        <v>91</v>
+      </c>
+      <c r="P164" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q164">
+        <v>3.25</v>
+      </c>
+      <c r="R164">
+        <v>2.25</v>
+      </c>
+      <c r="S164">
+        <v>3.1</v>
+      </c>
+      <c r="T164">
+        <v>1.33</v>
+      </c>
+      <c r="U164">
+        <v>3.25</v>
+      </c>
+      <c r="V164">
+        <v>2.63</v>
+      </c>
+      <c r="W164">
+        <v>1.44</v>
+      </c>
+      <c r="X164">
+        <v>7</v>
+      </c>
+      <c r="Y164">
+        <v>1.1</v>
+      </c>
+      <c r="Z164">
+        <v>2.85</v>
+      </c>
+      <c r="AA164">
+        <v>3.35</v>
+      </c>
+      <c r="AB164">
+        <v>2.45</v>
+      </c>
+      <c r="AC164">
+        <v>1.05</v>
+      </c>
+      <c r="AD164">
+        <v>12</v>
+      </c>
+      <c r="AE164">
+        <v>1.24</v>
+      </c>
+      <c r="AF164">
+        <v>3.92</v>
+      </c>
+      <c r="AG164">
+        <v>1.55</v>
+      </c>
+      <c r="AH164">
+        <v>2.4</v>
+      </c>
+      <c r="AI164">
+        <v>1.62</v>
+      </c>
+      <c r="AJ164">
+        <v>2.2</v>
+      </c>
+      <c r="AK164">
+        <v>1.51</v>
+      </c>
+      <c r="AL164">
+        <v>1.28</v>
+      </c>
+      <c r="AM164">
+        <v>1.46</v>
+      </c>
+      <c r="AN164">
+        <v>1.78</v>
+      </c>
+      <c r="AO164">
+        <v>1.89</v>
+      </c>
+      <c r="AP164">
+        <v>1.7</v>
+      </c>
+      <c r="AQ164">
+        <v>1.8</v>
+      </c>
+      <c r="AR164">
+        <v>1.55</v>
+      </c>
+      <c r="AS164">
+        <v>1.43</v>
+      </c>
+      <c r="AT164">
+        <v>2.98</v>
+      </c>
+      <c r="AU164">
+        <v>4</v>
+      </c>
+      <c r="AV164">
+        <v>5</v>
+      </c>
+      <c r="AW164">
+        <v>7</v>
+      </c>
+      <c r="AX164">
+        <v>8</v>
+      </c>
+      <c r="AY164">
+        <v>14</v>
+      </c>
+      <c r="AZ164">
+        <v>15</v>
+      </c>
+      <c r="BA164">
+        <v>4</v>
+      </c>
+      <c r="BB164">
+        <v>6</v>
+      </c>
+      <c r="BC164">
+        <v>10</v>
+      </c>
+      <c r="BD164">
+        <v>2.38</v>
+      </c>
+      <c r="BE164">
+        <v>6.5</v>
+      </c>
+      <c r="BF164">
+        <v>1.72</v>
+      </c>
+      <c r="BG164">
+        <v>1.26</v>
+      </c>
+      <c r="BH164">
+        <v>3.4</v>
+      </c>
+      <c r="BI164">
+        <v>1.43</v>
+      </c>
+      <c r="BJ164">
+        <v>2.55</v>
+      </c>
+      <c r="BK164">
+        <v>1.72</v>
+      </c>
+      <c r="BL164">
+        <v>1.98</v>
+      </c>
+      <c r="BM164">
+        <v>2.12</v>
+      </c>
+      <c r="BN164">
+        <v>1.63</v>
+      </c>
+      <c r="BO164">
+        <v>2.65</v>
+      </c>
+      <c r="BP164">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7466223</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45675.66666666666</v>
+      </c>
+      <c r="F165">
+        <v>19</v>
+      </c>
+      <c r="G165" t="s">
+        <v>86</v>
+      </c>
+      <c r="H165" t="s">
+        <v>71</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>1</v>
+      </c>
+      <c r="N165">
+        <v>2</v>
+      </c>
+      <c r="O165" t="s">
+        <v>132</v>
+      </c>
+      <c r="P165" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q165">
+        <v>7</v>
+      </c>
+      <c r="R165">
+        <v>2.4</v>
+      </c>
+      <c r="S165">
+        <v>1.91</v>
+      </c>
+      <c r="T165">
+        <v>1.33</v>
+      </c>
+      <c r="U165">
+        <v>3.25</v>
+      </c>
+      <c r="V165">
+        <v>2.5</v>
+      </c>
+      <c r="W165">
+        <v>1.5</v>
+      </c>
+      <c r="X165">
+        <v>6</v>
+      </c>
+      <c r="Y165">
+        <v>1.13</v>
+      </c>
+      <c r="Z165">
+        <v>8</v>
+      </c>
+      <c r="AA165">
+        <v>5</v>
+      </c>
+      <c r="AB165">
+        <v>1.35</v>
+      </c>
+      <c r="AC165">
+        <v>1.03</v>
+      </c>
+      <c r="AD165">
+        <v>15</v>
+      </c>
+      <c r="AE165">
+        <v>1.19</v>
+      </c>
+      <c r="AF165">
+        <v>4.45</v>
+      </c>
+      <c r="AG165">
+        <v>1.63</v>
+      </c>
+      <c r="AH165">
+        <v>2.23</v>
+      </c>
+      <c r="AI165">
+        <v>1.95</v>
+      </c>
+      <c r="AJ165">
+        <v>1.8</v>
+      </c>
+      <c r="AK165">
+        <v>2.85</v>
+      </c>
+      <c r="AL165">
+        <v>1.18</v>
+      </c>
+      <c r="AM165">
+        <v>1.1</v>
+      </c>
+      <c r="AN165">
+        <v>1.22</v>
+      </c>
+      <c r="AO165">
+        <v>2</v>
+      </c>
+      <c r="AP165">
+        <v>1.2</v>
+      </c>
+      <c r="AQ165">
+        <v>1.9</v>
+      </c>
+      <c r="AR165">
+        <v>1.19</v>
+      </c>
+      <c r="AS165">
+        <v>1.91</v>
+      </c>
+      <c r="AT165">
+        <v>3.1</v>
+      </c>
+      <c r="AU165">
+        <v>2</v>
+      </c>
+      <c r="AV165">
+        <v>8</v>
+      </c>
+      <c r="AW165">
+        <v>7</v>
+      </c>
+      <c r="AX165">
+        <v>8</v>
+      </c>
+      <c r="AY165">
+        <v>14</v>
+      </c>
+      <c r="AZ165">
+        <v>18</v>
+      </c>
+      <c r="BA165">
+        <v>3</v>
+      </c>
+      <c r="BB165">
+        <v>10</v>
+      </c>
+      <c r="BC165">
+        <v>13</v>
+      </c>
+      <c r="BD165">
+        <v>4.6</v>
+      </c>
+      <c r="BE165">
+        <v>8.5</v>
+      </c>
+      <c r="BF165">
+        <v>1.22</v>
+      </c>
+      <c r="BG165">
+        <v>1.24</v>
+      </c>
+      <c r="BH165">
+        <v>3.55</v>
+      </c>
+      <c r="BI165">
+        <v>1.41</v>
+      </c>
+      <c r="BJ165">
+        <v>2.63</v>
+      </c>
+      <c r="BK165">
+        <v>1.68</v>
+      </c>
+      <c r="BL165">
+        <v>2.04</v>
+      </c>
+      <c r="BM165">
+        <v>2.07</v>
+      </c>
+      <c r="BN165">
+        <v>1.66</v>
+      </c>
+      <c r="BO165">
+        <v>2.55</v>
+      </c>
+      <c r="BP165">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7466217</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45675.70833333334</v>
+      </c>
+      <c r="F166">
+        <v>19</v>
+      </c>
+      <c r="G166" t="s">
+        <v>77</v>
+      </c>
+      <c r="H166" t="s">
+        <v>70</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>3</v>
+      </c>
+      <c r="O166" t="s">
+        <v>203</v>
+      </c>
+      <c r="P166" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q166">
+        <v>2.2</v>
+      </c>
+      <c r="R166">
+        <v>2.3</v>
+      </c>
+      <c r="S166">
+        <v>5.5</v>
+      </c>
+      <c r="T166">
+        <v>1.36</v>
+      </c>
+      <c r="U166">
+        <v>3</v>
+      </c>
+      <c r="V166">
+        <v>2.63</v>
+      </c>
+      <c r="W166">
+        <v>1.44</v>
+      </c>
+      <c r="X166">
+        <v>7</v>
+      </c>
+      <c r="Y166">
+        <v>1.1</v>
+      </c>
+      <c r="Z166">
+        <v>1.57</v>
+      </c>
+      <c r="AA166">
+        <v>4</v>
+      </c>
+      <c r="AB166">
+        <v>5.75</v>
+      </c>
+      <c r="AC166">
+        <v>1.05</v>
+      </c>
+      <c r="AD166">
+        <v>12</v>
+      </c>
+      <c r="AE166">
+        <v>1.26</v>
+      </c>
+      <c r="AF166">
+        <v>3.67</v>
+      </c>
+      <c r="AG166">
+        <v>1.6</v>
+      </c>
+      <c r="AH166">
+        <v>2.3</v>
+      </c>
+      <c r="AI166">
+        <v>1.8</v>
+      </c>
+      <c r="AJ166">
+        <v>1.95</v>
+      </c>
+      <c r="AK166">
+        <v>1.15</v>
+      </c>
+      <c r="AL166">
+        <v>1.24</v>
+      </c>
+      <c r="AM166">
+        <v>2.25</v>
+      </c>
+      <c r="AN166">
+        <v>1.89</v>
+      </c>
+      <c r="AO166">
+        <v>0.5</v>
+      </c>
+      <c r="AP166">
+        <v>2</v>
+      </c>
+      <c r="AQ166">
+        <v>0.44</v>
+      </c>
+      <c r="AR166">
+        <v>1.78</v>
+      </c>
+      <c r="AS166">
+        <v>1.06</v>
+      </c>
+      <c r="AT166">
+        <v>2.84</v>
+      </c>
+      <c r="AU166">
+        <v>5</v>
+      </c>
+      <c r="AV166">
+        <v>6</v>
+      </c>
+      <c r="AW166">
+        <v>7</v>
+      </c>
+      <c r="AX166">
+        <v>17</v>
+      </c>
+      <c r="AY166">
+        <v>15</v>
+      </c>
+      <c r="AZ166">
+        <v>28</v>
+      </c>
+      <c r="BA166">
+        <v>2</v>
+      </c>
+      <c r="BB166">
+        <v>7</v>
+      </c>
+      <c r="BC166">
+        <v>9</v>
+      </c>
+      <c r="BD166">
+        <v>1.46</v>
+      </c>
+      <c r="BE166">
+        <v>6.75</v>
+      </c>
+      <c r="BF166">
+        <v>3.05</v>
+      </c>
+      <c r="BG166">
+        <v>1.29</v>
+      </c>
+      <c r="BH166">
+        <v>3.2</v>
+      </c>
+      <c r="BI166">
+        <v>1.49</v>
+      </c>
+      <c r="BJ166">
+        <v>2.4</v>
+      </c>
+      <c r="BK166">
+        <v>1.81</v>
+      </c>
+      <c r="BL166">
+        <v>1.88</v>
+      </c>
+      <c r="BM166">
+        <v>2.28</v>
+      </c>
+      <c r="BN166">
+        <v>1.55</v>
+      </c>
+      <c r="BO166">
+        <v>2.9</v>
+      </c>
+      <c r="BP166">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="289">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,12 @@
     <t>['5', '90+1']</t>
   </si>
   <si>
+    <t>['14', '20']</t>
+  </si>
+  <si>
+    <t>['34', '69', '71', '82']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -866,6 +872,15 @@
   </si>
   <si>
     <t>['25']</t>
+  </si>
+  <si>
+    <t>['28', '71']</t>
+  </si>
+  <si>
+    <t>['20', '82']</t>
+  </si>
+  <si>
+    <t>['39']</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP166"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1895,7 +1910,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1973,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2101,7 +2116,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2179,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ5">
         <v>1.8</v>
@@ -2307,7 +2322,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2388,7 +2403,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ6">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2591,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2925,7 +2940,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3006,7 +3021,7 @@
         <v>2</v>
       </c>
       <c r="AQ9">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3621,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>2.56</v>
@@ -4161,7 +4176,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4367,7 +4382,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4573,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5063,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ19">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5269,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>0.5600000000000001</v>
@@ -5397,7 +5412,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5475,7 +5490,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ21">
         <v>2.1</v>
@@ -5603,7 +5618,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5681,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ22">
         <v>2.56</v>
@@ -6221,7 +6236,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6299,7 +6314,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ25">
         <v>1.9</v>
@@ -6508,7 +6523,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR26">
         <v>1.73</v>
@@ -6633,7 +6648,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6917,7 +6932,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ28">
         <v>0.44</v>
@@ -7045,7 +7060,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7329,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>0.78</v>
@@ -7457,7 +7472,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7663,7 +7678,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -7744,7 +7759,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ32">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR32">
         <v>1.07</v>
@@ -7950,7 +7965,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
         <v>0.7</v>
@@ -8693,7 +8708,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -8977,10 +8992,10 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ38">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>0.83</v>
@@ -9105,7 +9120,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9311,7 +9326,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9389,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ40">
         <v>1.22</v>
@@ -9598,7 +9613,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -10216,7 +10231,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ44">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.45</v>
@@ -10341,7 +10356,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10547,7 +10562,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10753,7 +10768,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10959,7 +10974,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11040,7 +11055,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR48">
         <v>1.91</v>
@@ -11165,7 +11180,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11243,10 +11258,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR49">
         <v>1.18</v>
@@ -11371,7 +11386,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11449,7 +11464,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>0.44</v>
@@ -11577,7 +11592,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11655,10 +11670,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ51">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR51">
         <v>0.82</v>
@@ -11989,7 +12004,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12195,7 +12210,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12401,7 +12416,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12607,7 +12622,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -12685,7 +12700,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ56">
         <v>1.9</v>
@@ -12891,10 +12906,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ57">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13637,7 +13652,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13718,7 +13733,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR61">
         <v>1.5</v>
@@ -13843,7 +13858,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -14127,7 +14142,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ63">
         <v>1.22</v>
@@ -14333,7 +14348,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14667,7 +14682,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14748,7 +14763,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR66">
         <v>1.08</v>
@@ -14873,7 +14888,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -14954,7 +14969,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15160,7 +15175,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ68">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR68">
         <v>2.17</v>
@@ -15363,7 +15378,7 @@
         <v>0.33</v>
       </c>
       <c r="AP69">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>0.5600000000000001</v>
@@ -15491,7 +15506,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15903,7 +15918,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15981,7 +15996,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ72">
         <v>0.33</v>
@@ -16109,7 +16124,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16393,7 +16408,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ74">
         <v>0.6</v>
@@ -16521,7 +16536,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16602,7 +16617,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ75">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR75">
         <v>1.24</v>
@@ -16727,7 +16742,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17014,7 +17029,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.05</v>
@@ -17139,7 +17154,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17345,7 +17360,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17426,7 +17441,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ79">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR79">
         <v>1.54</v>
@@ -17551,7 +17566,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -17835,7 +17850,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -18375,7 +18390,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18453,10 +18468,10 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR84">
         <v>1.12</v>
@@ -18659,7 +18674,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18787,7 +18802,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19074,7 +19089,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR87">
         <v>1.97</v>
@@ -19405,7 +19420,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19611,7 +19626,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19692,7 +19707,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ90">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR90">
         <v>1.77</v>
@@ -19817,7 +19832,7 @@
         <v>91</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q91">
         <v>5.5</v>
@@ -19898,7 +19913,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR91">
         <v>1.05</v>
@@ -20229,7 +20244,7 @@
         <v>155</v>
       </c>
       <c r="P93" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20435,7 +20450,7 @@
         <v>156</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>2.05</v>
@@ -20847,7 +20862,7 @@
         <v>158</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
@@ -21131,7 +21146,7 @@
         <v>0.8</v>
       </c>
       <c r="AP97">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ97">
         <v>0.44</v>
@@ -21259,7 +21274,7 @@
         <v>160</v>
       </c>
       <c r="P98" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q98">
         <v>3.1</v>
@@ -21337,7 +21352,7 @@
         <v>2.5</v>
       </c>
       <c r="AP98">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ98">
         <v>2.56</v>
@@ -21752,7 +21767,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ100">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -22164,7 +22179,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ102">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22289,7 +22304,7 @@
         <v>91</v>
       </c>
       <c r="P103" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q103">
         <v>7.5</v>
@@ -22367,7 +22382,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ103">
         <v>2.1</v>
@@ -22495,7 +22510,7 @@
         <v>91</v>
       </c>
       <c r="P104" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q104">
         <v>4.33</v>
@@ -22701,7 +22716,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q105">
         <v>8.5</v>
@@ -22779,7 +22794,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ105">
         <v>1.9</v>
@@ -22907,7 +22922,7 @@
         <v>165</v>
       </c>
       <c r="P106" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q106">
         <v>3.1</v>
@@ -22988,7 +23003,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ106">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR106">
         <v>2.03</v>
@@ -23191,7 +23206,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>1.22</v>
@@ -23319,7 +23334,7 @@
         <v>115</v>
       </c>
       <c r="P108" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q108">
         <v>1.95</v>
@@ -23937,7 +23952,7 @@
         <v>169</v>
       </c>
       <c r="P111" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24018,7 +24033,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ111">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR111">
         <v>1.37</v>
@@ -24349,7 +24364,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24430,7 +24445,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR113">
         <v>1.21</v>
@@ -24555,7 +24570,7 @@
         <v>172</v>
       </c>
       <c r="P114" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -24633,7 +24648,7 @@
         <v>2.6</v>
       </c>
       <c r="AP114">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ114">
         <v>2.56</v>
@@ -24761,7 +24776,7 @@
         <v>93</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q115">
         <v>4</v>
@@ -24839,7 +24854,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ115">
         <v>1.8</v>
@@ -24967,7 +24982,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q116">
         <v>2.75</v>
@@ -25457,10 +25472,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR118">
         <v>1.65</v>
@@ -25663,7 +25678,7 @@
         <v>0.33</v>
       </c>
       <c r="AP119">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ119">
         <v>0.33</v>
@@ -26078,7 +26093,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ121">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.62</v>
@@ -26409,7 +26424,7 @@
         <v>178</v>
       </c>
       <c r="P123" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q123">
         <v>5</v>
@@ -26615,7 +26630,7 @@
         <v>179</v>
       </c>
       <c r="P124" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q124">
         <v>2.2</v>
@@ -26902,7 +26917,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ125">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR125">
         <v>1.92</v>
@@ -27027,7 +27042,7 @@
         <v>180</v>
       </c>
       <c r="P126" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q126">
         <v>4.75</v>
@@ -27105,10 +27120,10 @@
         <v>1.83</v>
       </c>
       <c r="AP126">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ126">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR126">
         <v>1.45</v>
@@ -27233,7 +27248,7 @@
         <v>181</v>
       </c>
       <c r="P127" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q127">
         <v>2.2</v>
@@ -27520,7 +27535,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ128">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR128">
         <v>2.46</v>
@@ -27851,7 +27866,7 @@
         <v>91</v>
       </c>
       <c r="P130" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q130">
         <v>2.6</v>
@@ -27929,7 +27944,7 @@
         <v>0.57</v>
       </c>
       <c r="AP130">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ130">
         <v>0.78</v>
@@ -28057,7 +28072,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q131">
         <v>8</v>
@@ -28263,7 +28278,7 @@
         <v>185</v>
       </c>
       <c r="P132" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q132">
         <v>3.25</v>
@@ -28344,7 +28359,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ132">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28675,7 +28690,7 @@
         <v>98</v>
       </c>
       <c r="P134" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28962,7 +28977,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ135">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR135">
         <v>1.92</v>
@@ -29087,7 +29102,7 @@
         <v>147</v>
       </c>
       <c r="P136" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>4.75</v>
@@ -29165,7 +29180,7 @@
         <v>2.43</v>
       </c>
       <c r="AP136">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ136">
         <v>2.56</v>
@@ -29293,7 +29308,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -29577,7 +29592,7 @@
         <v>2.63</v>
       </c>
       <c r="AP138">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
         <v>2.1</v>
@@ -29705,7 +29720,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q139">
         <v>2.2</v>
@@ -29786,7 +29801,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ139">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR139">
         <v>1.21</v>
@@ -29911,7 +29926,7 @@
         <v>189</v>
       </c>
       <c r="P140" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q140">
         <v>1.57</v>
@@ -29992,7 +30007,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ140">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR140">
         <v>1.81</v>
@@ -30117,7 +30132,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30401,7 +30416,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30941,7 +30956,7 @@
         <v>89</v>
       </c>
       <c r="P145" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q145">
         <v>4.33</v>
@@ -31019,7 +31034,7 @@
         <v>1.86</v>
       </c>
       <c r="AP145">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ145">
         <v>1.8</v>
@@ -31147,7 +31162,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -31637,7 +31652,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ148">
         <v>0.6</v>
@@ -31846,7 +31861,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ149">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR149">
         <v>1.83</v>
@@ -31971,7 +31986,7 @@
         <v>91</v>
       </c>
       <c r="P150" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q150">
         <v>4.75</v>
@@ -32049,10 +32064,10 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ150">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AR150">
         <v>1.58</v>
@@ -32383,7 +32398,7 @@
         <v>196</v>
       </c>
       <c r="P152" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q152">
         <v>2.25</v>
@@ -32464,7 +32479,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ152">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32795,7 +32810,7 @@
         <v>91</v>
       </c>
       <c r="P154" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q154">
         <v>3.5</v>
@@ -33001,7 +33016,7 @@
         <v>160</v>
       </c>
       <c r="P155" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33288,7 +33303,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ156">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR156">
         <v>1.73</v>
@@ -33413,7 +33428,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q157">
         <v>3.25</v>
@@ -33619,7 +33634,7 @@
         <v>199</v>
       </c>
       <c r="P158" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>1.83</v>
@@ -33825,7 +33840,7 @@
         <v>200</v>
       </c>
       <c r="P159" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -34237,7 +34252,7 @@
         <v>134</v>
       </c>
       <c r="P161" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q161">
         <v>2</v>
@@ -34443,7 +34458,7 @@
         <v>201</v>
       </c>
       <c r="P162" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34521,7 +34536,7 @@
         <v>0.33</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ162">
         <v>0.6</v>
@@ -34649,7 +34664,7 @@
         <v>202</v>
       </c>
       <c r="P163" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q163">
         <v>8</v>
@@ -35061,7 +35076,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35424,6 +35439,1036 @@
       </c>
       <c r="BP166">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7466219</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45676.34375</v>
+      </c>
+      <c r="F167">
+        <v>19</v>
+      </c>
+      <c r="G167" t="s">
+        <v>87</v>
+      </c>
+      <c r="H167" t="s">
+        <v>81</v>
+      </c>
+      <c r="I167">
+        <v>2</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>2</v>
+      </c>
+      <c r="L167">
+        <v>2</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>3</v>
+      </c>
+      <c r="O167" t="s">
+        <v>204</v>
+      </c>
+      <c r="P167" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q167">
+        <v>5</v>
+      </c>
+      <c r="R167">
+        <v>2.3</v>
+      </c>
+      <c r="S167">
+        <v>2.25</v>
+      </c>
+      <c r="T167">
+        <v>1.33</v>
+      </c>
+      <c r="U167">
+        <v>3.25</v>
+      </c>
+      <c r="V167">
+        <v>2.63</v>
+      </c>
+      <c r="W167">
+        <v>1.44</v>
+      </c>
+      <c r="X167">
+        <v>6.5</v>
+      </c>
+      <c r="Y167">
+        <v>1.11</v>
+      </c>
+      <c r="Z167">
+        <v>4.96</v>
+      </c>
+      <c r="AA167">
+        <v>4</v>
+      </c>
+      <c r="AB167">
+        <v>1.63</v>
+      </c>
+      <c r="AC167">
+        <v>1.03</v>
+      </c>
+      <c r="AD167">
+        <v>15</v>
+      </c>
+      <c r="AE167">
+        <v>1.22</v>
+      </c>
+      <c r="AF167">
+        <v>4.08</v>
+      </c>
+      <c r="AG167">
+        <v>1.66</v>
+      </c>
+      <c r="AH167">
+        <v>2.14</v>
+      </c>
+      <c r="AI167">
+        <v>1.7</v>
+      </c>
+      <c r="AJ167">
+        <v>2.05</v>
+      </c>
+      <c r="AK167">
+        <v>2.1</v>
+      </c>
+      <c r="AL167">
+        <v>1.24</v>
+      </c>
+      <c r="AM167">
+        <v>1.19</v>
+      </c>
+      <c r="AN167">
+        <v>1.67</v>
+      </c>
+      <c r="AO167">
+        <v>1.44</v>
+      </c>
+      <c r="AP167">
+        <v>1.8</v>
+      </c>
+      <c r="AQ167">
+        <v>1.3</v>
+      </c>
+      <c r="AR167">
+        <v>1.33</v>
+      </c>
+      <c r="AS167">
+        <v>1.51</v>
+      </c>
+      <c r="AT167">
+        <v>2.84</v>
+      </c>
+      <c r="AU167">
+        <v>5</v>
+      </c>
+      <c r="AV167">
+        <v>9</v>
+      </c>
+      <c r="AW167">
+        <v>9</v>
+      </c>
+      <c r="AX167">
+        <v>19</v>
+      </c>
+      <c r="AY167">
+        <v>19</v>
+      </c>
+      <c r="AZ167">
+        <v>34</v>
+      </c>
+      <c r="BA167">
+        <v>7</v>
+      </c>
+      <c r="BB167">
+        <v>7</v>
+      </c>
+      <c r="BC167">
+        <v>14</v>
+      </c>
+      <c r="BD167">
+        <v>2.95</v>
+      </c>
+      <c r="BE167">
+        <v>6.75</v>
+      </c>
+      <c r="BF167">
+        <v>1.48</v>
+      </c>
+      <c r="BG167">
+        <v>1.27</v>
+      </c>
+      <c r="BH167">
+        <v>3.3</v>
+      </c>
+      <c r="BI167">
+        <v>1.48</v>
+      </c>
+      <c r="BJ167">
+        <v>2.43</v>
+      </c>
+      <c r="BK167">
+        <v>1.79</v>
+      </c>
+      <c r="BL167">
+        <v>1.9</v>
+      </c>
+      <c r="BM167">
+        <v>2.23</v>
+      </c>
+      <c r="BN167">
+        <v>1.56</v>
+      </c>
+      <c r="BO167">
+        <v>2.9</v>
+      </c>
+      <c r="BP167">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7466215</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45676.4375</v>
+      </c>
+      <c r="F168">
+        <v>19</v>
+      </c>
+      <c r="G168" t="s">
+        <v>73</v>
+      </c>
+      <c r="H168" t="s">
+        <v>84</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>2</v>
+      </c>
+      <c r="N168">
+        <v>2</v>
+      </c>
+      <c r="O168" t="s">
+        <v>91</v>
+      </c>
+      <c r="P168" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q168">
+        <v>3.1</v>
+      </c>
+      <c r="R168">
+        <v>2.1</v>
+      </c>
+      <c r="S168">
+        <v>3.5</v>
+      </c>
+      <c r="T168">
+        <v>1.4</v>
+      </c>
+      <c r="U168">
+        <v>2.75</v>
+      </c>
+      <c r="V168">
+        <v>3</v>
+      </c>
+      <c r="W168">
+        <v>1.36</v>
+      </c>
+      <c r="X168">
+        <v>8</v>
+      </c>
+      <c r="Y168">
+        <v>1.08</v>
+      </c>
+      <c r="Z168">
+        <v>2.37</v>
+      </c>
+      <c r="AA168">
+        <v>3.35</v>
+      </c>
+      <c r="AB168">
+        <v>2.9</v>
+      </c>
+      <c r="AC168">
+        <v>1.04</v>
+      </c>
+      <c r="AD168">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE168">
+        <v>1.31</v>
+      </c>
+      <c r="AF168">
+        <v>3.35</v>
+      </c>
+      <c r="AG168">
+        <v>1.9</v>
+      </c>
+      <c r="AH168">
+        <v>1.84</v>
+      </c>
+      <c r="AI168">
+        <v>1.75</v>
+      </c>
+      <c r="AJ168">
+        <v>2</v>
+      </c>
+      <c r="AK168">
+        <v>1.38</v>
+      </c>
+      <c r="AL168">
+        <v>1.31</v>
+      </c>
+      <c r="AM168">
+        <v>1.57</v>
+      </c>
+      <c r="AN168">
+        <v>0.78</v>
+      </c>
+      <c r="AO168">
+        <v>0.5</v>
+      </c>
+      <c r="AP168">
+        <v>0.7</v>
+      </c>
+      <c r="AQ168">
+        <v>0.78</v>
+      </c>
+      <c r="AR168">
+        <v>1.26</v>
+      </c>
+      <c r="AS168">
+        <v>0.91</v>
+      </c>
+      <c r="AT168">
+        <v>2.17</v>
+      </c>
+      <c r="AU168">
+        <v>4</v>
+      </c>
+      <c r="AV168">
+        <v>4</v>
+      </c>
+      <c r="AW168">
+        <v>12</v>
+      </c>
+      <c r="AX168">
+        <v>6</v>
+      </c>
+      <c r="AY168">
+        <v>23</v>
+      </c>
+      <c r="AZ168">
+        <v>10</v>
+      </c>
+      <c r="BA168">
+        <v>6</v>
+      </c>
+      <c r="BB168">
+        <v>6</v>
+      </c>
+      <c r="BC168">
+        <v>12</v>
+      </c>
+      <c r="BD168">
+        <v>1.84</v>
+      </c>
+      <c r="BE168">
+        <v>6.75</v>
+      </c>
+      <c r="BF168">
+        <v>2.15</v>
+      </c>
+      <c r="BG168">
+        <v>1.24</v>
+      </c>
+      <c r="BH168">
+        <v>3.55</v>
+      </c>
+      <c r="BI168">
+        <v>1.41</v>
+      </c>
+      <c r="BJ168">
+        <v>2.63</v>
+      </c>
+      <c r="BK168">
+        <v>1.7</v>
+      </c>
+      <c r="BL168">
+        <v>2.02</v>
+      </c>
+      <c r="BM168">
+        <v>2.08</v>
+      </c>
+      <c r="BN168">
+        <v>1.65</v>
+      </c>
+      <c r="BO168">
+        <v>2.65</v>
+      </c>
+      <c r="BP168">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7466221</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45676.4375</v>
+      </c>
+      <c r="F169">
+        <v>19</v>
+      </c>
+      <c r="G169" t="s">
+        <v>80</v>
+      </c>
+      <c r="H169" t="s">
+        <v>78</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>2</v>
+      </c>
+      <c r="N169">
+        <v>2</v>
+      </c>
+      <c r="O169" t="s">
+        <v>91</v>
+      </c>
+      <c r="P169" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q169">
+        <v>5</v>
+      </c>
+      <c r="R169">
+        <v>2.4</v>
+      </c>
+      <c r="S169">
+        <v>2.1</v>
+      </c>
+      <c r="T169">
+        <v>1.3</v>
+      </c>
+      <c r="U169">
+        <v>3.4</v>
+      </c>
+      <c r="V169">
+        <v>2.5</v>
+      </c>
+      <c r="W169">
+        <v>1.5</v>
+      </c>
+      <c r="X169">
+        <v>6</v>
+      </c>
+      <c r="Y169">
+        <v>1.13</v>
+      </c>
+      <c r="Z169">
+        <v>5.05</v>
+      </c>
+      <c r="AA169">
+        <v>4.2</v>
+      </c>
+      <c r="AB169">
+        <v>1.59</v>
+      </c>
+      <c r="AC169">
+        <v>1.03</v>
+      </c>
+      <c r="AD169">
+        <v>17</v>
+      </c>
+      <c r="AE169">
+        <v>1.19</v>
+      </c>
+      <c r="AF169">
+        <v>4.45</v>
+      </c>
+      <c r="AG169">
+        <v>1.58</v>
+      </c>
+      <c r="AH169">
+        <v>2.29</v>
+      </c>
+      <c r="AI169">
+        <v>1.7</v>
+      </c>
+      <c r="AJ169">
+        <v>2.05</v>
+      </c>
+      <c r="AK169">
+        <v>2.4</v>
+      </c>
+      <c r="AL169">
+        <v>1.19</v>
+      </c>
+      <c r="AM169">
+        <v>1.16</v>
+      </c>
+      <c r="AN169">
+        <v>2.25</v>
+      </c>
+      <c r="AO169">
+        <v>1.89</v>
+      </c>
+      <c r="AP169">
+        <v>2</v>
+      </c>
+      <c r="AQ169">
+        <v>2</v>
+      </c>
+      <c r="AR169">
+        <v>1.56</v>
+      </c>
+      <c r="AS169">
+        <v>1.29</v>
+      </c>
+      <c r="AT169">
+        <v>2.85</v>
+      </c>
+      <c r="AU169">
+        <v>3</v>
+      </c>
+      <c r="AV169">
+        <v>11</v>
+      </c>
+      <c r="AW169">
+        <v>9</v>
+      </c>
+      <c r="AX169">
+        <v>9</v>
+      </c>
+      <c r="AY169">
+        <v>15</v>
+      </c>
+      <c r="AZ169">
+        <v>24</v>
+      </c>
+      <c r="BA169">
+        <v>5</v>
+      </c>
+      <c r="BB169">
+        <v>5</v>
+      </c>
+      <c r="BC169">
+        <v>10</v>
+      </c>
+      <c r="BD169">
+        <v>3.05</v>
+      </c>
+      <c r="BE169">
+        <v>6.5</v>
+      </c>
+      <c r="BF169">
+        <v>1.47</v>
+      </c>
+      <c r="BG169">
+        <v>1.41</v>
+      </c>
+      <c r="BH169">
+        <v>2.65</v>
+      </c>
+      <c r="BI169">
+        <v>1.71</v>
+      </c>
+      <c r="BJ169">
+        <v>2</v>
+      </c>
+      <c r="BK169">
+        <v>2.14</v>
+      </c>
+      <c r="BL169">
+        <v>1.62</v>
+      </c>
+      <c r="BM169">
+        <v>2.8</v>
+      </c>
+      <c r="BN169">
+        <v>1.37</v>
+      </c>
+      <c r="BO169">
+        <v>3.7</v>
+      </c>
+      <c r="BP169">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7466218</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45676.53125</v>
+      </c>
+      <c r="F170">
+        <v>19</v>
+      </c>
+      <c r="G170" t="s">
+        <v>72</v>
+      </c>
+      <c r="H170" t="s">
+        <v>79</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>2</v>
+      </c>
+      <c r="L170">
+        <v>4</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>5</v>
+      </c>
+      <c r="O170" t="s">
+        <v>205</v>
+      </c>
+      <c r="P170" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q170">
+        <v>2.5</v>
+      </c>
+      <c r="R170">
+        <v>2.2</v>
+      </c>
+      <c r="S170">
+        <v>4.5</v>
+      </c>
+      <c r="T170">
+        <v>1.4</v>
+      </c>
+      <c r="U170">
+        <v>2.75</v>
+      </c>
+      <c r="V170">
+        <v>2.75</v>
+      </c>
+      <c r="W170">
+        <v>1.4</v>
+      </c>
+      <c r="X170">
+        <v>8</v>
+      </c>
+      <c r="Y170">
+        <v>1.08</v>
+      </c>
+      <c r="Z170">
+        <v>1.85</v>
+      </c>
+      <c r="AA170">
+        <v>3.8</v>
+      </c>
+      <c r="AB170">
+        <v>3.5</v>
+      </c>
+      <c r="AC170">
+        <v>1.05</v>
+      </c>
+      <c r="AD170">
+        <v>12</v>
+      </c>
+      <c r="AE170">
+        <v>1.28</v>
+      </c>
+      <c r="AF170">
+        <v>3.52</v>
+      </c>
+      <c r="AG170">
+        <v>1.73</v>
+      </c>
+      <c r="AH170">
+        <v>2</v>
+      </c>
+      <c r="AI170">
+        <v>1.91</v>
+      </c>
+      <c r="AJ170">
+        <v>1.91</v>
+      </c>
+      <c r="AK170">
+        <v>1.23</v>
+      </c>
+      <c r="AL170">
+        <v>1.26</v>
+      </c>
+      <c r="AM170">
+        <v>1.93</v>
+      </c>
+      <c r="AN170">
+        <v>1.22</v>
+      </c>
+      <c r="AO170">
+        <v>1.11</v>
+      </c>
+      <c r="AP170">
+        <v>1.4</v>
+      </c>
+      <c r="AQ170">
+        <v>1</v>
+      </c>
+      <c r="AR170">
+        <v>1.58</v>
+      </c>
+      <c r="AS170">
+        <v>1.13</v>
+      </c>
+      <c r="AT170">
+        <v>2.71</v>
+      </c>
+      <c r="AU170">
+        <v>8</v>
+      </c>
+      <c r="AV170">
+        <v>3</v>
+      </c>
+      <c r="AW170">
+        <v>5</v>
+      </c>
+      <c r="AX170">
+        <v>7</v>
+      </c>
+      <c r="AY170">
+        <v>13</v>
+      </c>
+      <c r="AZ170">
+        <v>10</v>
+      </c>
+      <c r="BA170">
+        <v>2</v>
+      </c>
+      <c r="BB170">
+        <v>1</v>
+      </c>
+      <c r="BC170">
+        <v>3</v>
+      </c>
+      <c r="BD170">
+        <v>1.6</v>
+      </c>
+      <c r="BE170">
+        <v>6.75</v>
+      </c>
+      <c r="BF170">
+        <v>2.55</v>
+      </c>
+      <c r="BG170">
+        <v>1.2</v>
+      </c>
+      <c r="BH170">
+        <v>3.9</v>
+      </c>
+      <c r="BI170">
+        <v>1.37</v>
+      </c>
+      <c r="BJ170">
+        <v>2.8</v>
+      </c>
+      <c r="BK170">
+        <v>1.62</v>
+      </c>
+      <c r="BL170">
+        <v>2.14</v>
+      </c>
+      <c r="BM170">
+        <v>1.98</v>
+      </c>
+      <c r="BN170">
+        <v>1.72</v>
+      </c>
+      <c r="BO170">
+        <v>2.48</v>
+      </c>
+      <c r="BP170">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7466222</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45676.66666666666</v>
+      </c>
+      <c r="F171">
+        <v>19</v>
+      </c>
+      <c r="G171" t="s">
+        <v>75</v>
+      </c>
+      <c r="H171" t="s">
+        <v>83</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>2</v>
+      </c>
+      <c r="O171" t="s">
+        <v>133</v>
+      </c>
+      <c r="P171" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q171">
+        <v>2.05</v>
+      </c>
+      <c r="R171">
+        <v>2.5</v>
+      </c>
+      <c r="S171">
+        <v>5.5</v>
+      </c>
+      <c r="T171">
+        <v>1.29</v>
+      </c>
+      <c r="U171">
+        <v>3.5</v>
+      </c>
+      <c r="V171">
+        <v>2.25</v>
+      </c>
+      <c r="W171">
+        <v>1.57</v>
+      </c>
+      <c r="X171">
+        <v>5.5</v>
+      </c>
+      <c r="Y171">
+        <v>1.14</v>
+      </c>
+      <c r="Z171">
+        <v>1.5</v>
+      </c>
+      <c r="AA171">
+        <v>4.33</v>
+      </c>
+      <c r="AB171">
+        <v>5.5</v>
+      </c>
+      <c r="AC171">
+        <v>1.02</v>
+      </c>
+      <c r="AD171">
+        <v>17</v>
+      </c>
+      <c r="AE171">
+        <v>1.18</v>
+      </c>
+      <c r="AF171">
+        <v>4.65</v>
+      </c>
+      <c r="AG171">
+        <v>1.57</v>
+      </c>
+      <c r="AH171">
+        <v>2.3</v>
+      </c>
+      <c r="AI171">
+        <v>1.67</v>
+      </c>
+      <c r="AJ171">
+        <v>2.1</v>
+      </c>
+      <c r="AK171">
+        <v>1.14</v>
+      </c>
+      <c r="AL171">
+        <v>1.2</v>
+      </c>
+      <c r="AM171">
+        <v>2.45</v>
+      </c>
+      <c r="AN171">
+        <v>0.44</v>
+      </c>
+      <c r="AO171">
+        <v>0.22</v>
+      </c>
+      <c r="AP171">
+        <v>0.5</v>
+      </c>
+      <c r="AQ171">
+        <v>0.3</v>
+      </c>
+      <c r="AR171">
+        <v>1.53</v>
+      </c>
+      <c r="AS171">
+        <v>0.97</v>
+      </c>
+      <c r="AT171">
+        <v>2.5</v>
+      </c>
+      <c r="AU171">
+        <v>6</v>
+      </c>
+      <c r="AV171">
+        <v>6</v>
+      </c>
+      <c r="AW171">
+        <v>14</v>
+      </c>
+      <c r="AX171">
+        <v>14</v>
+      </c>
+      <c r="AY171">
+        <v>25</v>
+      </c>
+      <c r="AZ171">
+        <v>26</v>
+      </c>
+      <c r="BA171">
+        <v>6</v>
+      </c>
+      <c r="BB171">
+        <v>9</v>
+      </c>
+      <c r="BC171">
+        <v>15</v>
+      </c>
+      <c r="BD171">
+        <v>1.18</v>
+      </c>
+      <c r="BE171">
+        <v>9.5</v>
+      </c>
+      <c r="BF171">
+        <v>4.9</v>
+      </c>
+      <c r="BG171">
+        <v>1.11</v>
+      </c>
+      <c r="BH171">
+        <v>5.3</v>
+      </c>
+      <c r="BI171">
+        <v>1.22</v>
+      </c>
+      <c r="BJ171">
+        <v>3.7</v>
+      </c>
+      <c r="BK171">
+        <v>1.37</v>
+      </c>
+      <c r="BL171">
+        <v>2.8</v>
+      </c>
+      <c r="BM171">
+        <v>1.6</v>
+      </c>
+      <c r="BN171">
+        <v>2.17</v>
+      </c>
+      <c r="BO171">
+        <v>1.92</v>
+      </c>
+      <c r="BP171">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Netherlands Eredivisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="289">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -634,6 +634,9 @@
     <t>['34', '69', '71', '82']</t>
   </si>
   <si>
+    <t>['58']</t>
+  </si>
+  <si>
     <t>['8', '54']</t>
   </si>
   <si>
@@ -758,9 +761,6 @@
   </si>
   <si>
     <t>['6', '25']</t>
-  </si>
-  <si>
-    <t>['58']</t>
   </si>
   <si>
     <t>['18', '54']</t>
@@ -1242,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1910,7 +1910,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2116,7 +2116,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q5">
         <v>5.5</v>
@@ -2322,7 +2322,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>1.36</v>
@@ -2940,7 +2940,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q9">
         <v>2.6</v>
@@ -3639,7 +3639,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4176,7 +4176,7 @@
         <v>98</v>
       </c>
       <c r="P15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4382,7 +4382,7 @@
         <v>99</v>
       </c>
       <c r="P16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16">
         <v>2.1</v>
@@ -4588,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -5412,7 +5412,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q21">
         <v>11</v>
@@ -5618,7 +5618,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q22">
         <v>4.5</v>
@@ -5699,7 +5699,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ22">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR22">
         <v>0.79</v>
@@ -6108,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
         <v>1.22</v>
@@ -6236,7 +6236,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -6648,7 +6648,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7060,7 +7060,7 @@
         <v>91</v>
       </c>
       <c r="P29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -7472,7 +7472,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q31">
         <v>3.25</v>
@@ -7678,7 +7678,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q32">
         <v>3.4</v>
@@ -8708,7 +8708,7 @@
         <v>116</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q37">
         <v>6</v>
@@ -9120,7 +9120,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q39">
         <v>1.95</v>
@@ -9326,7 +9326,7 @@
         <v>119</v>
       </c>
       <c r="P40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q40">
         <v>2.63</v>
@@ -9816,7 +9816,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ42">
         <v>0.33</v>
@@ -10356,7 +10356,7 @@
         <v>123</v>
       </c>
       <c r="P45" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10562,7 +10562,7 @@
         <v>124</v>
       </c>
       <c r="P46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10768,7 +10768,7 @@
         <v>123</v>
       </c>
       <c r="P47" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>3.75</v>
@@ -10974,7 +10974,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>4</v>
@@ -11180,7 +11180,7 @@
         <v>94</v>
       </c>
       <c r="P49" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -11386,7 +11386,7 @@
         <v>126</v>
       </c>
       <c r="P50" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q50">
         <v>3.1</v>
@@ -11592,7 +11592,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -12004,7 +12004,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q53">
         <v>8.5</v>
@@ -12210,7 +12210,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12288,7 +12288,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ54">
         <v>0.6</v>
@@ -12416,7 +12416,7 @@
         <v>91</v>
       </c>
       <c r="P55" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>7.5</v>
@@ -12622,7 +12622,7 @@
         <v>106</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>5</v>
@@ -13652,7 +13652,7 @@
         <v>91</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q61">
         <v>6</v>
@@ -13858,7 +13858,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62">
         <v>2.1</v>
@@ -13939,7 +13939,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ62">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR62">
         <v>2.58</v>
@@ -14682,7 +14682,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q66">
         <v>1.83</v>
@@ -14888,7 +14888,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>2.2</v>
@@ -15506,7 +15506,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q70">
         <v>1.83</v>
@@ -15918,7 +15918,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16124,7 +16124,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q73">
         <v>4</v>
@@ -16536,7 +16536,7 @@
         <v>144</v>
       </c>
       <c r="P75" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q75">
         <v>6.5</v>
@@ -16742,7 +16742,7 @@
         <v>134</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>5</v>
@@ -17154,7 +17154,7 @@
         <v>91</v>
       </c>
       <c r="P78" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q78">
         <v>3.6</v>
@@ -17235,7 +17235,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ78">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR78">
         <v>1.07</v>
@@ -17360,7 +17360,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>6.5</v>
@@ -17438,7 +17438,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -17566,7 +17566,7 @@
         <v>134</v>
       </c>
       <c r="P80" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>2.6</v>
@@ -18390,7 +18390,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q84">
         <v>2.6</v>
@@ -18802,7 +18802,7 @@
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19626,7 +19626,7 @@
         <v>91</v>
       </c>
       <c r="P90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>2</v>
@@ -19832,7 +19832,7 @@
         <v>91</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="Q91">
         <v>5.5</v>
@@ -20116,7 +20116,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ92">
         <v>0.78</v>
@@ -21355,7 +21355,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ98">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR98">
         <v>1.7</v>
@@ -24030,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="AP111">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111">
         <v>0.3</v>
@@ -24651,7 +24651,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ114">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -27329,7 +27329,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ127">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR127">
         <v>1.82</v>
@@ -28356,7 +28356,7 @@
         <v>0.86</v>
       </c>
       <c r="AP132">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -29183,7 +29183,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ136">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29308,7 +29308,7 @@
         <v>91</v>
       </c>
       <c r="P137" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q137">
         <v>2.88</v>
@@ -31162,7 +31162,7 @@
         <v>139</v>
       </c>
       <c r="P146" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q146">
         <v>3.4</v>
@@ -33094,7 +33094,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ155">
         <v>1</v>
@@ -34333,7 +34333,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ161">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AR161">
         <v>1.8</v>
@@ -35076,7 +35076,7 @@
         <v>132</v>
       </c>
       <c r="P165" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q165">
         <v>7</v>
@@ -35488,7 +35488,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q167">
         <v>5</v>
@@ -36469,6 +36469,212 @@
       </c>
       <c r="BP171">
         <v>1.77</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7466230</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F172">
+        <v>20</v>
+      </c>
+      <c r="G172" t="s">
+        <v>84</v>
+      </c>
+      <c r="H172" t="s">
+        <v>76</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172" t="s">
+        <v>206</v>
+      </c>
+      <c r="P172" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q172">
+        <v>4</v>
+      </c>
+      <c r="R172">
+        <v>2.25</v>
+      </c>
+      <c r="S172">
+        <v>2.6</v>
+      </c>
+      <c r="T172">
+        <v>1.36</v>
+      </c>
+      <c r="U172">
+        <v>3</v>
+      </c>
+      <c r="V172">
+        <v>2.63</v>
+      </c>
+      <c r="W172">
+        <v>1.44</v>
+      </c>
+      <c r="X172">
+        <v>7</v>
+      </c>
+      <c r="Y172">
+        <v>1.1</v>
+      </c>
+      <c r="Z172">
+        <v>4.33</v>
+      </c>
+      <c r="AA172">
+        <v>3.87</v>
+      </c>
+      <c r="AB172">
+        <v>1.83</v>
+      </c>
+      <c r="AC172">
+        <v>1.03</v>
+      </c>
+      <c r="AD172">
+        <v>15</v>
+      </c>
+      <c r="AE172">
+        <v>1.22</v>
+      </c>
+      <c r="AF172">
+        <v>4.08</v>
+      </c>
+      <c r="AG172">
+        <v>1.81</v>
+      </c>
+      <c r="AH172">
+        <v>2.01</v>
+      </c>
+      <c r="AI172">
+        <v>1.67</v>
+      </c>
+      <c r="AJ172">
+        <v>2.1</v>
+      </c>
+      <c r="AK172">
+        <v>1.83</v>
+      </c>
+      <c r="AL172">
+        <v>1.26</v>
+      </c>
+      <c r="AM172">
+        <v>1.27</v>
+      </c>
+      <c r="AN172">
+        <v>1.22</v>
+      </c>
+      <c r="AO172">
+        <v>2.56</v>
+      </c>
+      <c r="AP172">
+        <v>1.2</v>
+      </c>
+      <c r="AQ172">
+        <v>2.4</v>
+      </c>
+      <c r="AR172">
+        <v>1.45</v>
+      </c>
+      <c r="AS172">
+        <v>1.24</v>
+      </c>
+      <c r="AT172">
+        <v>2.69</v>
+      </c>
+      <c r="AU172">
+        <v>4</v>
+      </c>
+      <c r="AV172">
+        <v>8</v>
+      </c>
+      <c r="AW172">
+        <v>8</v>
+      </c>
+      <c r="AX172">
+        <v>12</v>
+      </c>
+      <c r="AY172">
+        <v>13</v>
+      </c>
+      <c r="AZ172">
+        <v>25</v>
+      </c>
+      <c r="BA172">
+        <v>4</v>
+      </c>
+      <c r="BB172">
+        <v>10</v>
+      </c>
+      <c r="BC172">
+        <v>14</v>
+      </c>
+      <c r="BD172">
+        <v>2.55</v>
+      </c>
+      <c r="BE172">
+        <v>6.75</v>
+      </c>
+      <c r="BF172">
+        <v>1.58</v>
+      </c>
+      <c r="BG172">
+        <v>1.26</v>
+      </c>
+      <c r="BH172">
+        <v>3.4</v>
+      </c>
+      <c r="BI172">
+        <v>1.46</v>
+      </c>
+      <c r="BJ172">
+        <v>2.48</v>
+      </c>
+      <c r="BK172">
+        <v>1.74</v>
+      </c>
+      <c r="BL172">
+        <v>1.95</v>
+      </c>
+      <c r="BM172">
+        <v>2.17</v>
+      </c>
+      <c r="BN172">
+        <v>1.6</v>
+      </c>
+      <c r="BO172">
+        <v>2.8</v>
+      </c>
+      <c r="BP172">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>
